--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -9,10 +9,11 @@
     <sheet name="Business Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Executive Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Financial Plan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Quarterly Planner" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Strategy Plan" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="KPI Tracker" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Risks &amp; Actions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Monthly Costs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Quarterly Planner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Strategy Plan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="KPI Tracker" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Risks &amp; Actions" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -21,12 +22,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="168" formatCode="&quot;£&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -76,8 +79,41 @@
       <color rgb="FF37352F"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="000070C0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="001F2937"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="005B6573"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="0000205B"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -134,8 +170,38 @@
         <fgColor rgb="FFF7F1FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000205B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00287FA1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -312,11 +378,70 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D5DC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D5DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D5DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D5DC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9D5DC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9D5DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D5DC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9D5DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D5DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9D5DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D5DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D5DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -433,6 +558,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1197,19 +1417,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>Business Overview</t>
         </is>
@@ -1230,149 +1451,185 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Firm name</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>Duncan &amp; Co Financial</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="41" t="n"/>
-    </row>
-    <row r="7">
+      <c r="C6" s="52" t="n"/>
+      <c r="D6" s="52" t="n"/>
+      <c r="E6" s="52" t="n"/>
+      <c r="F6" s="52" t="n"/>
+      <c r="G6" s="52" t="n"/>
+      <c r="H6" s="53" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Previous firm / network</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="40" t="n"/>
-      <c r="E7" s="40" t="n"/>
-      <c r="F7" s="40" t="n"/>
-      <c r="G7" s="40" t="n"/>
-      <c r="H7" s="41" t="n"/>
-    </row>
-    <row r="8">
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>Rettie Financial Services Ltd / Carrington Mortgage UK Ltd (MAB appointed representative)</t>
+        </is>
+      </c>
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
+      <c r="E7" s="52" t="n"/>
+      <c r="F7" s="52" t="n"/>
+      <c r="G7" s="52" t="n"/>
+      <c r="H7" s="53" t="n"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Business address</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="40" t="n"/>
-      <c r="D8" s="40" t="n"/>
-      <c r="E8" s="40" t="n"/>
-      <c r="F8" s="40" t="n"/>
-      <c r="G8" s="40" t="n"/>
-      <c r="H8" s="41" t="n"/>
-    </row>
-    <row r="9">
+      <c r="B8" s="49" t="inlineStr">
+        <is>
+          <t>Edinburgh and East Lothian — meetings by appointment. Correspondence address TBC on incorporation. Robert.Duncan@duncanandcofinancial.co.uk | 07528523216</t>
+        </is>
+      </c>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
+      <c r="E8" s="52" t="n"/>
+      <c r="F8" s="52" t="n"/>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="53" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>FCA number</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="40" t="n"/>
-      <c r="D9" s="40" t="n"/>
-      <c r="E9" s="40" t="n"/>
-      <c r="F9" s="40" t="n"/>
-      <c r="G9" s="40" t="n"/>
-      <c r="H9" s="41" t="n"/>
-    </row>
-    <row r="10">
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>TBC — intending trading style under Rosemount Financial Solutions (IFA) Ltd FRN 535515</t>
+        </is>
+      </c>
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="52" t="n"/>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="53" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>MAB FCA number</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="40" t="n"/>
-      <c r="D10" s="40" t="n"/>
-      <c r="E10" s="40" t="n"/>
-      <c r="F10" s="40" t="n"/>
-      <c r="G10" s="40" t="n"/>
-      <c r="H10" s="41" t="n"/>
-    </row>
-    <row r="11">
+      <c r="B10" s="49" t="inlineStr">
+        <is>
+          <t>N/A going forward (previous network MAB Limited FRN 455545; MAB Derby 466154)</t>
+        </is>
+      </c>
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="52" t="n"/>
+      <c r="G10" s="52" t="n"/>
+      <c r="H10" s="53" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>L&amp;G master agency number</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="40" t="n"/>
-      <c r="D11" s="40" t="n"/>
-      <c r="E11" s="40" t="n"/>
-      <c r="F11" s="40" t="n"/>
-      <c r="G11" s="40" t="n"/>
-      <c r="H11" s="41" t="n"/>
-    </row>
-    <row r="12">
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="52" t="n"/>
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="52" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="53" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>MAB agency number</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="40" t="n"/>
-      <c r="D12" s="40" t="n"/>
-      <c r="E12" s="40" t="n"/>
-      <c r="F12" s="40" t="n"/>
-      <c r="G12" s="40" t="n"/>
-      <c r="H12" s="41" t="n"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="52" t="n"/>
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="52" t="n"/>
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="53" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Pipeline novated?</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="40" t="n"/>
-      <c r="E13" s="40" t="n"/>
-      <c r="F13" s="40" t="n"/>
-      <c r="G13" s="40" t="n"/>
-      <c r="H13" s="41" t="n"/>
-    </row>
-    <row r="14">
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>No — no personal client bank to novate</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="53" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Fee structure</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n"/>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="40" t="n"/>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="41" t="n"/>
-    </row>
-    <row r="15">
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Lender procuration + protection commission; client fees by agreement on complex / international cases</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="52" t="n"/>
+      <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="53" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Specialist licences required</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="40" t="n"/>
-      <c r="D15" s="40" t="n"/>
-      <c r="E15" s="40" t="n"/>
-      <c r="F15" s="40" t="n"/>
-      <c r="G15" s="40" t="n"/>
-      <c r="H15" s="41" t="n"/>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>CeMAP / Cert CII (MP). Later-life / equity release TBC with Rosemount</t>
+        </is>
+      </c>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="52" t="n"/>
+      <c r="F15" s="52" t="n"/>
+      <c r="G15" s="52" t="n"/>
+      <c r="H15" s="53" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
@@ -1423,37 +1680,133 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-    </row>
-    <row r="23">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>Robert (Bob) Duncan</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="inlineStr">
+        <is>
+          <t>Director / Key Individual</t>
+        </is>
+      </c>
+      <c r="C20" s="50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D20" s="50" t="inlineStr">
+        <is>
+          <t>Self-employed</t>
+        </is>
+      </c>
+      <c r="E20" s="50" t="inlineStr">
+        <is>
+          <t>Edinburgh / East Lothian</t>
+        </is>
+      </c>
+      <c r="F20" s="50" t="inlineStr">
+        <is>
+          <t>CeMAP / Cert CII (MP)</t>
+        </is>
+      </c>
+      <c r="G20" s="50" t="inlineStr">
+        <is>
+          <t>Self (launch)</t>
+        </is>
+      </c>
+      <c r="H20" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="49" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>Admin / Case Manager (future)</t>
+        </is>
+      </c>
+      <c r="C21" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D21" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E21" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F21" s="50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="H21" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="49" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="inlineStr">
+        <is>
+          <t>Adviser — AR transition (future)</t>
+        </is>
+      </c>
+      <c r="C22" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D22" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E22" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F22" s="50" t="inlineStr">
+        <is>
+          <t>CeMAP TBC</t>
+        </is>
+      </c>
+      <c r="G22" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="H22" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="36" t="n"/>
       <c r="B23" s="36" t="n"/>
       <c r="C23" s="36" t="n"/>
@@ -1463,7 +1816,7 @@
       <c r="G23" s="36" t="n"/>
       <c r="H23" s="36" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="36" t="n"/>
       <c r="C24" s="36" t="n"/>
@@ -1473,7 +1826,7 @@
       <c r="G24" s="36" t="n"/>
       <c r="H24" s="36" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="36" t="n"/>
       <c r="B25" s="36" t="n"/>
       <c r="C25" s="36" t="n"/>
@@ -1483,7 +1836,7 @@
       <c r="G25" s="36" t="n"/>
       <c r="H25" s="36" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="36" t="n"/>
       <c r="C26" s="36" t="n"/>
@@ -1493,7 +1846,7 @@
       <c r="G26" s="36" t="n"/>
       <c r="H26" s="36" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="36" t="n"/>
       <c r="B27" s="36" t="n"/>
       <c r="C27" s="36" t="n"/>
@@ -1503,7 +1856,7 @@
       <c r="G27" s="36" t="n"/>
       <c r="H27" s="36" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="18" customHeight="1">
       <c r="A28" s="36" t="n"/>
       <c r="B28" s="36" t="n"/>
       <c r="C28" s="36" t="n"/>
@@ -1513,7 +1866,7 @@
       <c r="G28" s="36" t="n"/>
       <c r="H28" s="36" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="18" customHeight="1">
       <c r="A29" s="36" t="n"/>
       <c r="B29" s="36" t="n"/>
       <c r="C29" s="36" t="n"/>
@@ -1523,7 +1876,7 @@
       <c r="G29" s="36" t="n"/>
       <c r="H29" s="36" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="18" customHeight="1">
       <c r="A30" s="36" t="n"/>
       <c r="B30" s="36" t="n"/>
       <c r="C30" s="36" t="n"/>
@@ -1533,7 +1886,7 @@
       <c r="G30" s="36" t="n"/>
       <c r="H30" s="36" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="18" customHeight="1">
       <c r="A31" s="36" t="n"/>
       <c r="B31" s="36" t="n"/>
       <c r="C31" s="36" t="n"/>
@@ -1582,71 +1935,263 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="36" t="n"/>
-      <c r="B36" s="36" t="n"/>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="36" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="36" t="n"/>
-      <c r="B37" s="36" t="n"/>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="36" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="36" t="n"/>
-      <c r="B38" s="36" t="n"/>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="36" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="36" t="n"/>
-      <c r="B39" s="36" t="n"/>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="36" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="36" t="n"/>
-      <c r="B40" s="36" t="n"/>
-      <c r="C40" s="36" t="n"/>
-      <c r="D40" s="36" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="36" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="36" t="n"/>
-      <c r="B41" s="36" t="n"/>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="36" t="n"/>
-      <c r="E41" s="14" t="n"/>
-      <c r="F41" s="36" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="36" t="n"/>
-      <c r="B42" s="36" t="n"/>
-      <c r="C42" s="36" t="n"/>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="36" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>DJ Alexander / David Alexander</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="inlineStr">
+        <is>
+          <t>Email / phone introduction</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="inlineStr">
+        <is>
+          <t>Estate agency</t>
+        </is>
+      </c>
+      <c r="D36" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E36" s="51" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F36" s="49" t="inlineStr">
+        <is>
+          <t>Primary introducer Edinburgh &amp; Glasgow</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <t>Hannah Fraser</t>
+        </is>
+      </c>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>Email / phone introduction</t>
+        </is>
+      </c>
+      <c r="C37" s="49" t="inlineStr">
+        <is>
+          <t>Solicitor / property</t>
+        </is>
+      </c>
+      <c r="D37" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E37" s="51" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F37" s="49" t="inlineStr">
+        <is>
+          <t>Senior property partner; agreed primary Edinburgh introducer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>Ralph’s Thayer (Ivan Ralph)</t>
+        </is>
+      </c>
+      <c r="B38" s="49" t="inlineStr">
+        <is>
+          <t>Referral partnership outreach</t>
+        </is>
+      </c>
+      <c r="C38" s="49" t="inlineStr">
+        <is>
+          <t>Referral partner</t>
+        </is>
+      </c>
+      <c r="D38" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E38" s="51" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F38" s="49" t="inlineStr">
+        <is>
+          <t>Outreach 2 Sep 2026 — not yet live</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>Glasgow letting / estate agency (via DJ Alexander)</t>
+        </is>
+      </c>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>IF confirmed — exclusive</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>Estate / lettings</t>
+        </is>
+      </c>
+      <c r="D39" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E39" s="51" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F39" s="49" t="inlineStr">
+        <is>
+          <t>~2,000–3,000 homes/year discussed; NOT confirmed; high risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="49" t="inlineStr">
+        <is>
+          <t>Website / PPC</t>
+        </is>
+      </c>
+      <c r="B40" s="49" t="inlineStr">
+        <is>
+          <t>Web form</t>
+        </is>
+      </c>
+      <c r="C40" s="49" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="D40" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E40" s="51" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F40" s="49" t="inlineStr">
+        <is>
+          <t>Contact Business Gateway for build funding (3 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>BoE rate-triggered CRM emails</t>
+        </is>
+      </c>
+      <c r="B41" s="49" t="inlineStr">
+        <is>
+          <t>Email campaign (hold / cut / rise)</t>
+        </is>
+      </c>
+      <c r="C41" s="49" t="inlineStr">
+        <is>
+          <t>Own CRM</t>
+        </is>
+      </c>
+      <c r="D41" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E41" s="51" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F41" s="49" t="inlineStr">
+        <is>
+          <t>Intelligent Office sequences; drafted 26 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>Accountant introductions</t>
+        </is>
+      </c>
+      <c r="B42" s="49" t="inlineStr">
+        <is>
+          <t>Professional referral</t>
+        </is>
+      </c>
+      <c r="C42" s="49" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="D42" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E42" s="51" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F42" s="49" t="inlineStr">
+        <is>
+          <t>Via self-employed / complex cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>International / overseas buyers</t>
+        </is>
+      </c>
+      <c r="B43" s="49" t="inlineStr">
+        <is>
+          <t>Introducer / website</t>
+        </is>
+      </c>
+      <c r="C43" s="49" t="inlineStr">
+        <is>
+          <t>Specialist</t>
+        </is>
+      </c>
+      <c r="D43" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E43" s="51" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F43" s="49" t="inlineStr">
+        <is>
+          <t>Edinburgh &amp; St Andrews demand; compliance still to agree with Rosemount</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
       <c r="A44" s="36" t="n"/>
       <c r="B44" s="36" t="n"/>
       <c r="C44" s="36" t="n"/>
@@ -1654,7 +2199,7 @@
       <c r="E44" s="14" t="n"/>
       <c r="F44" s="36" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="18" customHeight="1">
       <c r="A45" s="36" t="n"/>
       <c r="B45" s="36" t="n"/>
       <c r="C45" s="36" t="n"/>
@@ -1662,7 +2207,7 @@
       <c r="E45" s="14" t="n"/>
       <c r="F45" s="36" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="18" customHeight="1">
       <c r="A46" s="36" t="n"/>
       <c r="B46" s="36" t="n"/>
       <c r="C46" s="36" t="n"/>
@@ -1670,7 +2215,7 @@
       <c r="E46" s="14" t="n"/>
       <c r="F46" s="36" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="18" customHeight="1">
       <c r="A47" s="36" t="n"/>
       <c r="B47" s="36" t="n"/>
       <c r="C47" s="36" t="n"/>
@@ -1701,7 +2246,8 @@
       <formula1>"Employed,Self-employed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1709,7 +2255,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
@@ -1723,7 +2269,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>2027 Strategic Business Plan</t>
         </is>
@@ -1951,35 +2497,51 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Firm name</t>
         </is>
       </c>
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>Duncan &amp; Co Financial</t>
         </is>
       </c>
-    </row>
-    <row r="18">
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
+      <c r="E17" s="52" t="n"/>
+      <c r="F17" s="53" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Plan owner</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n"/>
-    </row>
-    <row r="19">
+      <c r="B18" s="49" t="inlineStr">
+        <is>
+          <t>Robert (Bob) Duncan</t>
+        </is>
+      </c>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="n"/>
+      <c r="E18" s="52" t="n"/>
+      <c r="F18" s="53" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Version date</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
-        <v>46253</v>
-      </c>
+      <c r="B19" s="54" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
+      <c r="E19" s="52" t="n"/>
+      <c r="F19" s="53" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2296,21 +2858,25 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="15">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:N2"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="B19:F19"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A4:C5"/>
     <mergeCell ref="E4:G5"/>
     <mergeCell ref="I4:K5"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="M4:N5"/>
     <mergeCell ref="I6:K6"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2319,7 +2885,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
@@ -2331,7 +2897,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>2027 Financial Plan</t>
         </is>
@@ -2422,19 +2988,19 @@
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
+      <c r="B9" s="55" t="n">
+        <v>1500</v>
       </c>
       <c r="C9" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="38" t="inlineStr">
-        <is>
-          <t>Wealth, GI, Later Life, conveyancing, wills and other referrals</t>
-        </is>
-      </c>
-      <c r="E9" s="40" t="n"/>
-      <c r="F9" s="41" t="n"/>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t>GI, referrals and Beanstalk JISA starter — overwrite if needed</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="53" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -2953,339 +3519,2295 @@
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00287FA1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <dimension ref="A1:P84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
-        <is>
-          <t>Quarterly Planner</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Annual Goals</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Achieve £15.3m written target</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Confirm objectives and KPI ownership</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>Review Q1 performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Deliver £12.42m Mortgage written</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Complete business and team information</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>Adjust pipeline and lead-source mix</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Deliver £2.88m Protection written</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Launch Mortgage and Protection priorities</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Execute client-bank growth actions</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Build Other Income from Wealth, GI, Later Life and referrals</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Agree Other Income targets and referral routes</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Review recruitment and capacity</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Complete adviser recruitment and capability plan</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Review Q1 performance</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>Review Q2 performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="15" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="E10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="15" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="E11" s="15" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="15" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="E12" s="15" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="15" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="E13" s="15" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="15" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="E14" s="15" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="15" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="E15" s="15" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="15" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="E16" s="15" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="15" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="E17" s="15" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="15" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="E18" s="15" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="15" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="E19" s="15" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="15" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="15" t="n"/>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>Monthly Costs — Bob Duncan / Duncan &amp; Co Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1"/>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="59" t="inlineStr">
+        <is>
+          <t>Yellow cells are editable. Confirmed network terms are from the 2 Sep 2026 Rosemount meeting (Ahmed Bawa). Do not treat Financial Plan protection written (£240,000/month) as cash. Tesla lease, website and most operating lines are estimates for Bob to overwrite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>1. Confirmed network terms (Rosemount / Rosemount Financial Solutions)</t>
+        </is>
+      </c>
+      <c r="B5" s="52" t="n"/>
+      <c r="C5" s="52" t="n"/>
+      <c r="D5" s="52" t="n"/>
+      <c r="E5" s="53" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="62" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B6" s="62" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C6" s="62" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D6" s="62" t="inlineStr">
+        <is>
+          <t>Source / notes</t>
+        </is>
+      </c>
+      <c r="E6" s="62" t="inlineStr">
+        <is>
+          <t>Linked calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="63" t="inlineStr">
+        <is>
+          <t>Weekly Rosemount fee</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="n">
+        <v>75</v>
+      </c>
+      <c r="C7" s="50" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>£75/week covers FCA, PI and software (2 Sep 2026).</t>
+        </is>
+      </c>
+      <c r="E7" s="56" t="inlineStr">
+        <is>
+          <t>Confirmed commercial term</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="63" t="inlineStr">
+        <is>
+          <t>Weeks per year (for monthly conversion)</t>
+        </is>
+      </c>
+      <c r="B8" s="65" t="n">
+        <v>52</v>
+      </c>
+      <c r="C8" s="50" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="inlineStr">
+        <is>
+          <t>Standard 52-week year.</t>
+        </is>
+      </c>
+      <c r="E8" s="56" t="inlineStr">
+        <is>
+          <t>Used in monthly fee formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="63" t="inlineStr">
+        <is>
+          <t>Monthly Rosemount fee</t>
+        </is>
+      </c>
+      <c r="B9" s="66">
+        <f>$B$7*$B$8/12</f>
+        <v/>
+      </c>
+      <c r="C9" s="67" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t>75 × 52 / 12. Confirmed from weekly term.</t>
+        </is>
+      </c>
+      <c r="E9" s="56" t="inlineStr">
+        <is>
+          <t>75*52/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="63" t="inlineStr">
+        <is>
+          <t>Mortgage net retention (network share)</t>
+        </is>
+      </c>
+      <c r="B10" s="68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C10" s="50" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>Bob keeps 90% of mortgage procuration.</t>
+        </is>
+      </c>
+      <c r="E10" s="56" t="inlineStr">
+        <is>
+          <t>10% net retention mortgages</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Protection net retention (network share)</t>
+        </is>
+      </c>
+      <c r="B11" s="68" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C11" s="50" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="inlineStr">
+        <is>
+          <t>Bob keeps 85% of protection commission.</t>
+        </is>
+      </c>
+      <c r="E11" s="56" t="inlineStr">
+        <is>
+          <t>15% net retention protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Mortgage procuration fee %</t>
+        </is>
+      </c>
+      <c r="B12" s="69" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="inlineStr">
+        <is>
+          <t>Overwrite with actual lender mix. Not a Rosemount quote.</t>
+        </is>
+      </c>
+      <c r="E12" s="56" t="inlineStr">
+        <is>
+          <t>Used in cash bridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>Protection cash commission (monthly, before retention)</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C13" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>Cash assumption — NOT the £240k protection written figure.</t>
+        </is>
+      </c>
+      <c r="E13" s="56" t="inlineStr">
+        <is>
+          <t>Used in cash bridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>Year-1 income ambition (low)</t>
+        </is>
+      </c>
+      <c r="B14" s="70" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C14" s="50" t="inlineStr">
+        <is>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t>20 Aug 2026 structure consult.</t>
+        </is>
+      </c>
+      <c r="E14" s="56" t="inlineStr">
+        <is>
+          <t>Ambition range</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Year-1 income ambition (high)</t>
+        </is>
+      </c>
+      <c r="B15" s="70" t="n">
+        <v>120000</v>
+      </c>
+      <c r="C15" s="50" t="inlineStr">
+        <is>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t>20 Aug 2026 structure consult.</t>
+        </is>
+      </c>
+      <c r="E15" s="56" t="inlineStr">
+        <is>
+          <t>Ambition range</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Financial Plan mortgage / protection lag (months)</t>
+        </is>
+      </c>
+      <c r="B16" s="71">
+        <f>'Financial Plan'!C7</f>
+        <v/>
+      </c>
+      <c r="C16" s="67" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t>Written work banks on a lag. Used in the 12-month cash view.</t>
+        </is>
+      </c>
+      <c r="E16" s="56" t="inlineStr">
+        <is>
+          <t>Financial Plan C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="60" t="inlineStr">
+        <is>
+          <t>2. Monthly operating costs</t>
+        </is>
+      </c>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="n"/>
+      <c r="E18" s="52" t="n"/>
+      <c r="F18" s="53" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="62" t="inlineStr">
+        <is>
+          <t>Cost item</t>
+        </is>
+      </c>
+      <c r="B19" s="62" t="inlineStr">
+        <is>
+          <t>Monthly £</t>
+        </is>
+      </c>
+      <c r="C19" s="62" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D19" s="62" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E19" s="62" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F19" s="62" t="inlineStr">
+        <is>
+          <t>Annual £</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="63" t="inlineStr">
+        <is>
+          <t>Rosemount network fee</t>
+        </is>
+      </c>
+      <c r="B20" s="66">
+        <f>$B$9</f>
+        <v/>
+      </c>
+      <c r="C20" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D20" s="67" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="E20" s="56" t="inlineStr">
+        <is>
+          <t>From weekly £75 term (FCA, PI, software).</t>
+        </is>
+      </c>
+      <c r="F20" s="66">
+        <f>B20*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="63" t="inlineStr">
+        <is>
+          <t>Tesla Model Y lease</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="n">
+        <v>550</v>
+      </c>
+      <c r="C21" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D21" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E21" s="56" t="inlineStr">
+        <is>
+          <t>Amount UNKNOWN — 3 years remaining. Transfer needs lessor approval.</t>
+        </is>
+      </c>
+      <c r="F21" s="66">
+        <f>B21*12</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="15" t="n"/>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="15" t="n"/>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>Review Q2 performance</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>Review Q3 performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="15" t="n"/>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>Accelerate client-bank and Other Income activity</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>Close annual Mortgage and Protection gaps</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="15" t="n"/>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>Refresh risks and KPI actions</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>Complete year-end campaigns</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="15" t="n"/>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>Confirm Q4 closing priorities</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>Finalise 2028 objectives and budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="15" t="n"/>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>Review Q3 performance</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>Hold annual planning review</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="15" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="E28" s="21" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="15" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="E29" s="21" t="n"/>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="15" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="E30" s="21" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="15" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="E31" s="21" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="15" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="E32" s="21" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="15" t="n"/>
-      <c r="C33" s="19" t="n"/>
-      <c r="E33" s="21" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="15" t="n"/>
-      <c r="C34" s="19" t="n"/>
-      <c r="E34" s="21" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="15" t="n"/>
-      <c r="C35" s="19" t="n"/>
-      <c r="E35" s="21" t="n"/>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="15" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="E36" s="21" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="15" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="E37" s="21" t="n"/>
+      <c r="A22" s="63" t="inlineStr">
+        <is>
+          <t>EV insurance</t>
+        </is>
+      </c>
+      <c r="B22" s="64" t="n">
+        <v>80</v>
+      </c>
+      <c r="C22" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D22" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E22" s="56" t="inlineStr">
+        <is>
+          <t>Overwrite with actual schedule.</t>
+        </is>
+      </c>
+      <c r="F22" s="66">
+        <f>B22*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="63" t="inlineStr">
+        <is>
+          <t>Home / destination charging</t>
+        </is>
+      </c>
+      <c r="B23" s="64" t="n">
+        <v>80</v>
+      </c>
+      <c r="C23" s="50" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D23" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E23" s="56" t="inlineStr">
+        <is>
+          <t>Electricity for the Tesla; will vary.</t>
+        </is>
+      </c>
+      <c r="F23" s="66">
+        <f>B23*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="63" t="inlineStr">
+        <is>
+          <t>Mobile phone</t>
+        </is>
+      </c>
+      <c r="B24" s="64" t="n">
+        <v>45</v>
+      </c>
+      <c r="C24" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D24" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E24" s="56" t="inlineStr">
+        <is>
+          <t>Business mobile.</t>
+        </is>
+      </c>
+      <c r="F24" s="66">
+        <f>B24*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="63" t="inlineStr">
+        <is>
+          <t>Broadband share</t>
+        </is>
+      </c>
+      <c r="B25" s="64" t="n">
+        <v>30</v>
+      </c>
+      <c r="C25" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D25" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E25" s="56" t="inlineStr">
+        <is>
+          <t>Home-office share.</t>
+        </is>
+      </c>
+      <c r="F25" s="66">
+        <f>B25*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="63" t="inlineStr">
+        <is>
+          <t>Microsoft 365</t>
+        </is>
+      </c>
+      <c r="B26" s="64" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D26" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E26" s="56" t="inlineStr">
+        <is>
+          <t>Business standard / equivalent.</t>
+        </is>
+      </c>
+      <c r="F26" s="66">
+        <f>B26*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="63" t="inlineStr">
+        <is>
+          <t>Xero</t>
+        </is>
+      </c>
+      <c r="B27" s="64" t="n">
+        <v>33</v>
+      </c>
+      <c r="C27" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D27" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E27" s="56" t="inlineStr">
+        <is>
+          <t>Bookkeeping subscription.</t>
+        </is>
+      </c>
+      <c r="F27" s="66">
+        <f>B27*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="63" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="B28" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="C28" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D28" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E28" s="56" t="inlineStr">
+        <is>
+          <t>Monthly accrual; year-end extra not included.</t>
+        </is>
+      </c>
+      <c r="F28" s="66">
+        <f>B28*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="63" t="inlineStr">
+        <is>
+          <t>Domain / email</t>
+        </is>
+      </c>
+      <c r="B29" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="C29" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D29" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E29" s="56" t="inlineStr">
+        <is>
+          <t>duncanandcofinancial.co.uk.</t>
+        </is>
+      </c>
+      <c r="F29" s="66">
+        <f>B29*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="63" t="inlineStr">
+        <is>
+          <t>Web hosting</t>
+        </is>
+      </c>
+      <c r="B30" s="64" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D30" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E30" s="56" t="inlineStr">
+        <is>
+          <t>If not bundled with the website grant.</t>
+        </is>
+      </c>
+      <c r="F30" s="66">
+        <f>B30*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="63" t="inlineStr">
+        <is>
+          <t>AI / productivity tools</t>
+        </is>
+      </c>
+      <c r="B31" s="64" t="n">
+        <v>40</v>
+      </c>
+      <c r="C31" s="50" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D31" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E31" s="56" t="inlineStr">
+        <is>
+          <t>Grok / Cursor / similar.</t>
+        </is>
+      </c>
+      <c r="F31" s="66">
+        <f>B31*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="63" t="inlineStr">
+        <is>
+          <t>Marketing / PPC / print</t>
+        </is>
+      </c>
+      <c r="B32" s="64" t="n">
+        <v>150</v>
+      </c>
+      <c r="C32" s="50" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D32" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E32" s="56" t="inlineStr">
+        <is>
+          <t>Light brand and lead support.</t>
+        </is>
+      </c>
+      <c r="F32" s="66">
+        <f>B32*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="63" t="inlineStr">
+        <is>
+          <t>Client gifts / thank-yous</t>
+        </is>
+      </c>
+      <c r="B33" s="64" t="n">
+        <v>40</v>
+      </c>
+      <c r="C33" s="50" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D33" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E33" s="56" t="inlineStr">
+        <is>
+          <t>Keep modest in year 1.</t>
+        </is>
+      </c>
+      <c r="F33" s="66">
+        <f>B33*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="63" t="inlineStr">
+        <is>
+          <t>Business bank</t>
+        </is>
+      </c>
+      <c r="B34" s="64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D34" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E34" s="56" t="inlineStr">
+        <is>
+          <t>Account fees.</t>
+        </is>
+      </c>
+      <c r="F34" s="66">
+        <f>B34*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="63" t="inlineStr">
+        <is>
+          <t>CII membership / CPD</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="n">
+        <v>20</v>
+      </c>
+      <c r="C35" s="50" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D35" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E35" s="56" t="inlineStr">
+        <is>
+          <t>Cert CII (MP) ongoing.</t>
+        </is>
+      </c>
+      <c r="F35" s="66">
+        <f>B35*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="63" t="inlineStr">
+        <is>
+          <t>Stationery / postage</t>
+        </is>
+      </c>
+      <c r="B36" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="C36" s="50" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D36" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E36" s="56" t="inlineStr">
+        <is>
+          <t>IDV, packs, post.</t>
+        </is>
+      </c>
+      <c r="F36" s="66">
+        <f>B36*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="63" t="inlineStr">
+        <is>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" s="50" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D37" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E37" s="56" t="inlineStr">
+        <is>
+          <t>Buffer for forgotten small costs.</t>
+        </is>
+      </c>
+      <c r="F37" s="66">
+        <f>B37*12</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="15" t="n"/>
-      <c r="C38" s="19" t="n"/>
-      <c r="E38" s="21" t="n"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="15" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="E39" s="21" t="n"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="15" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="E40" s="21" t="n"/>
+      <c r="A38" s="72" t="inlineStr">
+        <is>
+          <t>TOTAL monthly operating costs</t>
+        </is>
+      </c>
+      <c r="B38" s="73">
+        <f>SUM(B20:B37)</f>
+        <v/>
+      </c>
+      <c r="C38" s="67" t="inlineStr"/>
+      <c r="D38" s="67" t="inlineStr"/>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>Updates when any yellow monthly amount changes.</t>
+        </is>
+      </c>
+      <c r="F38" s="73">
+        <f>B38*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="60" t="inlineStr">
+        <is>
+          <t>3. One-off launch costs (not in the monthly run-rate)</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+      <c r="E40" s="52" t="n"/>
+      <c r="F40" s="53" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="62" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B41" s="62" t="inlineStr">
+        <is>
+          <t>Amount £</t>
+        </is>
+      </c>
+      <c r="C41" s="62" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D41" s="62" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E41" s="62" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F41" s="62" t="inlineStr">
+        <is>
+          <t>In 12-month cash view?</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="63" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="B42" s="70" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C42" s="50" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="D42" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E42" s="56" t="inlineStr">
+        <is>
+          <t>Replace / dedicated work machine.</t>
+        </is>
+      </c>
+      <c r="F42" s="56" t="inlineStr">
+        <is>
+          <t>Jan cash outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>Website build</t>
+        </is>
+      </c>
+      <c r="B43" s="70" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C43" s="50" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="D43" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E43" s="56" t="inlineStr">
+        <is>
+          <t>Or Business Gateway funded — set to 0 if grant covers it.</t>
+        </is>
+      </c>
+      <c r="F43" s="56" t="inlineStr">
+        <is>
+          <t>Jan cash outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>Company formation</t>
+        </is>
+      </c>
+      <c r="B44" s="70" t="n">
+        <v>50</v>
+      </c>
+      <c r="C44" s="50" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="D44" s="50" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="E44" s="56" t="inlineStr">
+        <is>
+          <t>If limited company route is chosen (20 Aug consult).</t>
+        </is>
+      </c>
+      <c r="F44" s="56" t="inlineStr">
+        <is>
+          <t>Jan cash outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>Branding / ID / cards</t>
+        </is>
+      </c>
+      <c r="B45" s="70" t="n"/>
+      <c r="C45" s="50" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="D45" s="50" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="E45" s="56" t="inlineStr">
+        <is>
+          <t>Leave blank until quoted.</t>
+        </is>
+      </c>
+      <c r="F45" s="56" t="inlineStr">
+        <is>
+          <t>Jan cash outflow if entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="72" t="inlineStr">
+        <is>
+          <t>TOTAL one-off launch costs</t>
+        </is>
+      </c>
+      <c r="B46" s="74">
+        <f>SUM(B42:B45)</f>
+        <v/>
+      </c>
+      <c r="C46" s="67" t="inlineStr"/>
+      <c r="D46" s="67" t="inlineStr"/>
+      <c r="E46" s="67" t="inlineStr">
+        <is>
+          <t>Website may be grant-funded — overwrite B43 to 0 if so.</t>
+        </is>
+      </c>
+      <c r="F46" s="74">
+        <f>B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="60" t="inlineStr">
+        <is>
+          <t>4. Cash income bridge (steady-state month — written is not cash)</t>
+        </is>
+      </c>
+      <c r="B48" s="52" t="n"/>
+      <c r="C48" s="52" t="n"/>
+      <c r="D48" s="52" t="n"/>
+      <c r="E48" s="52" t="n"/>
+      <c r="F48" s="53" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="62" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B49" s="62" t="inlineStr">
+        <is>
+          <t>Monthly £</t>
+        </is>
+      </c>
+      <c r="C49" s="62" t="inlineStr">
+        <is>
+          <t>Annual £</t>
+        </is>
+      </c>
+      <c r="D49" s="62" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E49" s="62" t="inlineStr">
+        <is>
+          <t>Formula / source</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="63" t="inlineStr">
+        <is>
+          <t>Mortgage written (Financial Plan default)</t>
+        </is>
+      </c>
+      <c r="B50" s="75">
+        <f>'Financial Plan'!B7</f>
+        <v/>
+      </c>
+      <c r="C50" s="75">
+        <f>B50*12</f>
+        <v/>
+      </c>
+      <c r="D50" s="56" t="inlineStr">
+        <is>
+          <t>Written lending, not cash. Kept as the plan target.</t>
+        </is>
+      </c>
+      <c r="E50" s="56" t="inlineStr">
+        <is>
+          <t>Financial Plan B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>Mortgage cash commission</t>
+        </is>
+      </c>
+      <c r="B51" s="66">
+        <f>B50*$B$12*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="C51" s="66">
+        <f>C50*$B$12*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="D51" s="56" t="inlineStr">
+        <is>
+          <t>Written × proc % × (1 − 10% retention).</t>
+        </is>
+      </c>
+      <c r="E51" s="56" t="inlineStr">
+        <is>
+          <t>B50 × B12 × (1−B10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="63" t="inlineStr">
+        <is>
+          <t>Protection cash commission (after retention)</t>
+        </is>
+      </c>
+      <c r="B52" s="66">
+        <f>$B$13*(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="C52" s="66">
+        <f>B52*12</f>
+        <v/>
+      </c>
+      <c r="D52" s="56" t="inlineStr">
+        <is>
+          <t>Uses the £3,000 cash assumption — not £240k written.</t>
+        </is>
+      </c>
+      <c r="E52" s="56" t="inlineStr">
+        <is>
+          <t>B13 × (1−B11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="63" t="inlineStr">
+        <is>
+          <t>Other Income (Financial Plan default)</t>
+        </is>
+      </c>
+      <c r="B53" s="66">
+        <f>'Financial Plan'!B9</f>
+        <v/>
+      </c>
+      <c r="C53" s="66">
+        <f>B53*12</f>
+        <v/>
+      </c>
+      <c r="D53" s="56" t="inlineStr">
+        <is>
+          <t>GI / referrals / Beanstalk starter (£1,500).</t>
+        </is>
+      </c>
+      <c r="E53" s="56" t="inlineStr">
+        <is>
+          <t>Financial Plan B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="72" t="inlineStr">
+        <is>
+          <t>TOTAL cash in</t>
+        </is>
+      </c>
+      <c r="B54" s="73">
+        <f>B51+B52+B53</f>
+        <v/>
+      </c>
+      <c r="C54" s="73">
+        <f>C51+C52+C53</f>
+        <v/>
+      </c>
+      <c r="D54" s="56" t="inlineStr">
+        <is>
+          <t>Steady-state, before operating costs.</t>
+        </is>
+      </c>
+      <c r="E54" s="56" t="inlineStr">
+        <is>
+          <t>Sum of cash lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="63" t="inlineStr">
+        <is>
+          <t>Monthly operating costs</t>
+        </is>
+      </c>
+      <c r="B55" s="66">
+        <f>B38</f>
+        <v/>
+      </c>
+      <c r="C55" s="66">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="D55" s="56" t="inlineStr">
+        <is>
+          <t>From section 2 total.</t>
+        </is>
+      </c>
+      <c r="E55" s="56" t="inlineStr">
+        <is>
+          <t>B38</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="72" t="inlineStr">
+        <is>
+          <t>Net cash (steady-state)</t>
+        </is>
+      </c>
+      <c r="B56" s="73">
+        <f>B54-B55</f>
+        <v/>
+      </c>
+      <c r="C56" s="73">
+        <f>C54-C55</f>
+        <v/>
+      </c>
+      <c r="D56" s="56" t="inlineStr">
+        <is>
+          <t>Compare with the £80–120k ambition.</t>
+        </is>
+      </c>
+      <c r="E56" s="56" t="inlineStr">
+        <is>
+          <t>Cash in − opex</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>Ambition low (£80,000)</t>
+        </is>
+      </c>
+      <c r="B57" s="66">
+        <f>$B$14/12</f>
+        <v/>
+      </c>
+      <c r="C57" s="66">
+        <f>$B$14</f>
+        <v/>
+      </c>
+      <c r="D57" s="56" t="inlineStr">
+        <is>
+          <t>20 Aug consult — low end.</t>
+        </is>
+      </c>
+      <c r="E57" s="56" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="63" t="inlineStr">
+        <is>
+          <t>Ambition high (£120,000)</t>
+        </is>
+      </c>
+      <c r="B58" s="66">
+        <f>$B$15/12</f>
+        <v/>
+      </c>
+      <c r="C58" s="66">
+        <f>$B$15</f>
+        <v/>
+      </c>
+      <c r="D58" s="56" t="inlineStr">
+        <is>
+          <t>20 Aug consult — high end.</t>
+        </is>
+      </c>
+      <c r="E58" s="56" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="72" t="inlineStr">
+        <is>
+          <t>Gap vs low ambition</t>
+        </is>
+      </c>
+      <c r="B59" s="73">
+        <f>B56-B57</f>
+        <v/>
+      </c>
+      <c r="C59" s="73">
+        <f>C56-C57</f>
+        <v/>
+      </c>
+      <c r="D59" s="56" t="inlineStr">
+        <is>
+          <t>Negative means the current assumptions miss £80k.</t>
+        </is>
+      </c>
+      <c r="E59" s="56" t="inlineStr">
+        <is>
+          <t>Net − low ambition</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="72" t="inlineStr">
+        <is>
+          <t>Gap vs high ambition</t>
+        </is>
+      </c>
+      <c r="B60" s="73">
+        <f>B56-B58</f>
+        <v/>
+      </c>
+      <c r="C60" s="73">
+        <f>C56-C58</f>
+        <v/>
+      </c>
+      <c r="D60" s="56" t="inlineStr">
+        <is>
+          <t>Shows how far the current mix is from £120k.</t>
+        </is>
+      </c>
+      <c r="E60" s="56" t="inlineStr">
+        <is>
+          <t>Net − high ambition</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="60" t="inlineStr">
+        <is>
+          <t>5. 2027 twelve-month cost / net cash view (2-month lag on mortgage and protection cash)</t>
+        </is>
+      </c>
+      <c r="B63" s="52" t="n"/>
+      <c r="C63" s="52" t="n"/>
+      <c r="D63" s="52" t="n"/>
+      <c r="E63" s="52" t="n"/>
+      <c r="F63" s="52" t="n"/>
+      <c r="G63" s="52" t="n"/>
+      <c r="H63" s="52" t="n"/>
+      <c r="I63" s="52" t="n"/>
+      <c r="J63" s="52" t="n"/>
+      <c r="K63" s="52" t="n"/>
+      <c r="L63" s="52" t="n"/>
+      <c r="M63" s="52" t="n"/>
+      <c r="N63" s="52" t="n"/>
+      <c r="O63" s="52" t="n"/>
+      <c r="P63" s="53" t="n"/>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="62" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B64" s="62" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C64" s="62" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D64" s="62" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E64" s="62" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F64" s="62" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G64" s="62" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H64" s="62" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I64" s="62" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J64" s="62" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K64" s="62" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L64" s="62" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M64" s="62" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N64" s="62" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="63" t="inlineStr">
+        <is>
+          <t>Mortgage written (Financial Plan)</t>
+        </is>
+      </c>
+      <c r="B65" s="75">
+        <f>'Financial Plan'!D13</f>
+        <v/>
+      </c>
+      <c r="C65" s="75">
+        <f>'Financial Plan'!E13</f>
+        <v/>
+      </c>
+      <c r="D65" s="75">
+        <f>'Financial Plan'!F13</f>
+        <v/>
+      </c>
+      <c r="E65" s="75">
+        <f>'Financial Plan'!G13</f>
+        <v/>
+      </c>
+      <c r="F65" s="75">
+        <f>'Financial Plan'!H13</f>
+        <v/>
+      </c>
+      <c r="G65" s="75">
+        <f>'Financial Plan'!I13</f>
+        <v/>
+      </c>
+      <c r="H65" s="75">
+        <f>'Financial Plan'!J13</f>
+        <v/>
+      </c>
+      <c r="I65" s="75">
+        <f>'Financial Plan'!K13</f>
+        <v/>
+      </c>
+      <c r="J65" s="75">
+        <f>'Financial Plan'!L13</f>
+        <v/>
+      </c>
+      <c r="K65" s="75">
+        <f>'Financial Plan'!M13</f>
+        <v/>
+      </c>
+      <c r="L65" s="75">
+        <f>'Financial Plan'!N13</f>
+        <v/>
+      </c>
+      <c r="M65" s="75">
+        <f>'Financial Plan'!O13</f>
+        <v/>
+      </c>
+      <c r="N65" s="75">
+        <f>SUM(B65:M65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="63" t="inlineStr">
+        <is>
+          <t>Mortgage cash (after 10% retention, lagged)</t>
+        </is>
+      </c>
+      <c r="B66" s="66">
+        <f>IF(1&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,1-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="C66" s="66">
+        <f>IF(2&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,2-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="D66" s="66">
+        <f>IF(3&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,3-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="E66" s="66">
+        <f>IF(4&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,4-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="F66" s="66">
+        <f>IF(5&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,5-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="G66" s="66">
+        <f>IF(6&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,6-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="H66" s="66">
+        <f>IF(7&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,7-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="I66" s="66">
+        <f>IF(8&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,8-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="J66" s="66">
+        <f>IF(9&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,9-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="K66" s="66">
+        <f>IF(10&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,10-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="L66" s="66">
+        <f>IF(11&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,11-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="M66" s="66">
+        <f>IF(12&lt;=$B$16,0,INDEX('Financial Plan'!$D$13:$O$13,12-$B$16)*$B$12*(1-$B$10))</f>
+        <v/>
+      </c>
+      <c r="N66" s="66">
+        <f>SUM(B66:M66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="63" t="inlineStr">
+        <is>
+          <t>Protection cash (after 15% retention, lagged)</t>
+        </is>
+      </c>
+      <c r="B67" s="66">
+        <f>IF(1&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="C67" s="66">
+        <f>IF(2&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="D67" s="66">
+        <f>IF(3&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="E67" s="66">
+        <f>IF(4&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="F67" s="66">
+        <f>IF(5&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="G67" s="66">
+        <f>IF(6&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="H67" s="66">
+        <f>IF(7&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="I67" s="66">
+        <f>IF(8&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="J67" s="66">
+        <f>IF(9&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="K67" s="66">
+        <f>IF(10&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="L67" s="66">
+        <f>IF(11&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="M67" s="66">
+        <f>IF(12&lt;=$B$16,0,$B$13*(1-$B$11))</f>
+        <v/>
+      </c>
+      <c r="N67" s="66">
+        <f>SUM(B67:M67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>Other Income (Financial Plan)</t>
+        </is>
+      </c>
+      <c r="B68" s="66">
+        <f>'Financial Plan'!D15</f>
+        <v/>
+      </c>
+      <c r="C68" s="66">
+        <f>'Financial Plan'!E15</f>
+        <v/>
+      </c>
+      <c r="D68" s="66">
+        <f>'Financial Plan'!F15</f>
+        <v/>
+      </c>
+      <c r="E68" s="66">
+        <f>'Financial Plan'!G15</f>
+        <v/>
+      </c>
+      <c r="F68" s="66">
+        <f>'Financial Plan'!H15</f>
+        <v/>
+      </c>
+      <c r="G68" s="66">
+        <f>'Financial Plan'!I15</f>
+        <v/>
+      </c>
+      <c r="H68" s="66">
+        <f>'Financial Plan'!J15</f>
+        <v/>
+      </c>
+      <c r="I68" s="66">
+        <f>'Financial Plan'!K15</f>
+        <v/>
+      </c>
+      <c r="J68" s="66">
+        <f>'Financial Plan'!L15</f>
+        <v/>
+      </c>
+      <c r="K68" s="66">
+        <f>'Financial Plan'!M15</f>
+        <v/>
+      </c>
+      <c r="L68" s="66">
+        <f>'Financial Plan'!N15</f>
+        <v/>
+      </c>
+      <c r="M68" s="66">
+        <f>'Financial Plan'!O15</f>
+        <v/>
+      </c>
+      <c r="N68" s="66">
+        <f>SUM(B68:M68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="72" t="inlineStr">
+        <is>
+          <t>Total cash in</t>
+        </is>
+      </c>
+      <c r="B69" s="73">
+        <f>B66+B67+B68</f>
+        <v/>
+      </c>
+      <c r="C69" s="73">
+        <f>C66+C67+C68</f>
+        <v/>
+      </c>
+      <c r="D69" s="73">
+        <f>D66+D67+D68</f>
+        <v/>
+      </c>
+      <c r="E69" s="73">
+        <f>E66+E67+E68</f>
+        <v/>
+      </c>
+      <c r="F69" s="73">
+        <f>F66+F67+F68</f>
+        <v/>
+      </c>
+      <c r="G69" s="73">
+        <f>G66+G67+G68</f>
+        <v/>
+      </c>
+      <c r="H69" s="73">
+        <f>H66+H67+H68</f>
+        <v/>
+      </c>
+      <c r="I69" s="73">
+        <f>I66+I67+I68</f>
+        <v/>
+      </c>
+      <c r="J69" s="73">
+        <f>J66+J67+J68</f>
+        <v/>
+      </c>
+      <c r="K69" s="73">
+        <f>K66+K67+K68</f>
+        <v/>
+      </c>
+      <c r="L69" s="73">
+        <f>L66+L67+L68</f>
+        <v/>
+      </c>
+      <c r="M69" s="73">
+        <f>M66+M67+M68</f>
+        <v/>
+      </c>
+      <c r="N69" s="73">
+        <f>SUM(B69:M69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="63" t="inlineStr">
+        <is>
+          <t>Operating costs</t>
+        </is>
+      </c>
+      <c r="B70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="C70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="D70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="E70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="F70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="G70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="H70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="I70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="J70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="K70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="L70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="M70" s="66">
+        <f>$B$38</f>
+        <v/>
+      </c>
+      <c r="N70" s="66">
+        <f>SUM(B70:M70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="63" t="inlineStr">
+        <is>
+          <t>One-off launch costs (Jan)</t>
+        </is>
+      </c>
+      <c r="B71" s="75">
+        <f>$B$46</f>
+        <v/>
+      </c>
+      <c r="C71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="75">
+        <f>SUM(B71:M71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="72" t="inlineStr">
+        <is>
+          <t>Net cash</t>
+        </is>
+      </c>
+      <c r="B72" s="73">
+        <f>B69-B70-B71</f>
+        <v/>
+      </c>
+      <c r="C72" s="73">
+        <f>C69-C70-C71</f>
+        <v/>
+      </c>
+      <c r="D72" s="73">
+        <f>D69-D70-D71</f>
+        <v/>
+      </c>
+      <c r="E72" s="73">
+        <f>E69-E70-E71</f>
+        <v/>
+      </c>
+      <c r="F72" s="73">
+        <f>F69-F70-F71</f>
+        <v/>
+      </c>
+      <c r="G72" s="73">
+        <f>G69-G70-G71</f>
+        <v/>
+      </c>
+      <c r="H72" s="73">
+        <f>H69-H70-H71</f>
+        <v/>
+      </c>
+      <c r="I72" s="73">
+        <f>I69-I70-I71</f>
+        <v/>
+      </c>
+      <c r="J72" s="73">
+        <f>J69-J70-J71</f>
+        <v/>
+      </c>
+      <c r="K72" s="73">
+        <f>K69-K70-K71</f>
+        <v/>
+      </c>
+      <c r="L72" s="73">
+        <f>L69-L70-L71</f>
+        <v/>
+      </c>
+      <c r="M72" s="73">
+        <f>M69-M70-M71</f>
+        <v/>
+      </c>
+      <c r="N72" s="73">
+        <f>SUM(B72:M72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="72" t="inlineStr">
+        <is>
+          <t>Cumulative net cash</t>
+        </is>
+      </c>
+      <c r="B73" s="73">
+        <f>B72</f>
+        <v/>
+      </c>
+      <c r="C73" s="73">
+        <f>B73+C72</f>
+        <v/>
+      </c>
+      <c r="D73" s="73">
+        <f>C73+D72</f>
+        <v/>
+      </c>
+      <c r="E73" s="73">
+        <f>D73+E72</f>
+        <v/>
+      </c>
+      <c r="F73" s="73">
+        <f>E73+F72</f>
+        <v/>
+      </c>
+      <c r="G73" s="73">
+        <f>F73+G72</f>
+        <v/>
+      </c>
+      <c r="H73" s="73">
+        <f>G73+H72</f>
+        <v/>
+      </c>
+      <c r="I73" s="73">
+        <f>H73+I72</f>
+        <v/>
+      </c>
+      <c r="J73" s="73">
+        <f>I73+J72</f>
+        <v/>
+      </c>
+      <c r="K73" s="73">
+        <f>J73+K72</f>
+        <v/>
+      </c>
+      <c r="L73" s="73">
+        <f>K73+L72</f>
+        <v/>
+      </c>
+      <c r="M73" s="73">
+        <f>L73+M72</f>
+        <v/>
+      </c>
+      <c r="N73" s="73">
+        <f>M73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="60" t="inlineStr">
+        <is>
+          <t>6. Notes for Bob</t>
+        </is>
+      </c>
+      <c r="B75" s="52" t="n"/>
+      <c r="C75" s="52" t="n"/>
+      <c r="D75" s="52" t="n"/>
+      <c r="E75" s="52" t="n"/>
+      <c r="F75" s="52" t="n"/>
+      <c r="G75" s="52" t="n"/>
+      <c r="H75" s="52" t="n"/>
+      <c r="I75" s="52" t="n"/>
+      <c r="J75" s="52" t="n"/>
+      <c r="K75" s="52" t="n"/>
+      <c r="L75" s="52" t="n"/>
+      <c r="M75" s="52" t="n"/>
+      <c r="N75" s="52" t="n"/>
+      <c r="O75" s="52" t="n"/>
+      <c r="P75" s="53" t="n"/>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="56" t="inlineStr">
+        <is>
+          <t>Tesla Model Y lease amount is unknown — the £550 line is an estimate. Overwrite B21. Transfer to a company needs lessor approval.</t>
+        </is>
+      </c>
+      <c r="B76" s="52" t="n"/>
+      <c r="C76" s="52" t="n"/>
+      <c r="D76" s="52" t="n"/>
+      <c r="E76" s="52" t="n"/>
+      <c r="F76" s="52" t="n"/>
+      <c r="G76" s="52" t="n"/>
+      <c r="H76" s="52" t="n"/>
+      <c r="I76" s="52" t="n"/>
+      <c r="J76" s="52" t="n"/>
+      <c r="K76" s="52" t="n"/>
+      <c r="L76" s="52" t="n"/>
+      <c r="M76" s="52" t="n"/>
+      <c r="N76" s="52" t="n"/>
+      <c r="O76" s="52" t="n"/>
+      <c r="P76" s="53" t="n"/>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="77" t="inlineStr">
+        <is>
+          <t>Website build (~£2,500) may be Business Gateway funded (3 Sep 2026). Set B43 to 0 if a grant covers it.</t>
+        </is>
+      </c>
+      <c r="B77" s="52" t="n"/>
+      <c r="C77" s="52" t="n"/>
+      <c r="D77" s="52" t="n"/>
+      <c r="E77" s="52" t="n"/>
+      <c r="F77" s="52" t="n"/>
+      <c r="G77" s="52" t="n"/>
+      <c r="H77" s="52" t="n"/>
+      <c r="I77" s="52" t="n"/>
+      <c r="J77" s="52" t="n"/>
+      <c r="K77" s="52" t="n"/>
+      <c r="L77" s="52" t="n"/>
+      <c r="M77" s="52" t="n"/>
+      <c r="N77" s="52" t="n"/>
+      <c r="O77" s="52" t="n"/>
+      <c r="P77" s="53" t="n"/>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="56" t="inlineStr">
+        <is>
+          <t>First-year cash is tight until introducers convert. Rosemount (2 Sep): the first year is the hardest — stay proactive on activity.</t>
+        </is>
+      </c>
+      <c r="B78" s="52" t="n"/>
+      <c r="C78" s="52" t="n"/>
+      <c r="D78" s="52" t="n"/>
+      <c r="E78" s="52" t="n"/>
+      <c r="F78" s="52" t="n"/>
+      <c r="G78" s="52" t="n"/>
+      <c r="H78" s="52" t="n"/>
+      <c r="I78" s="52" t="n"/>
+      <c r="J78" s="52" t="n"/>
+      <c r="K78" s="52" t="n"/>
+      <c r="L78" s="52" t="n"/>
+      <c r="M78" s="52" t="n"/>
+      <c r="N78" s="52" t="n"/>
+      <c r="O78" s="52" t="n"/>
+      <c r="P78" s="53" t="n"/>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="77" t="inlineStr">
+        <is>
+          <t>Yellow cells are for you to overwrite: FCA number once appointed (Business Overview), Tesla lease, lead volumes, close rates, L&amp;G if any, proc %, protection cash, and every estimate cost.</t>
+        </is>
+      </c>
+      <c r="B79" s="52" t="n"/>
+      <c r="C79" s="52" t="n"/>
+      <c r="D79" s="52" t="n"/>
+      <c r="E79" s="52" t="n"/>
+      <c r="F79" s="52" t="n"/>
+      <c r="G79" s="52" t="n"/>
+      <c r="H79" s="52" t="n"/>
+      <c r="I79" s="52" t="n"/>
+      <c r="J79" s="52" t="n"/>
+      <c r="K79" s="52" t="n"/>
+      <c r="L79" s="52" t="n"/>
+      <c r="M79" s="52" t="n"/>
+      <c r="N79" s="52" t="n"/>
+      <c r="O79" s="52" t="n"/>
+      <c r="P79" s="53" t="n"/>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="56" t="inlineStr">
+        <is>
+          <t>Protection written £240,000/month on the Financial Plan is a written target, not a cash figure. Cash uses the £3,000/month assumption after 15% retention.</t>
+        </is>
+      </c>
+      <c r="B80" s="52" t="n"/>
+      <c r="C80" s="52" t="n"/>
+      <c r="D80" s="52" t="n"/>
+      <c r="E80" s="52" t="n"/>
+      <c r="F80" s="52" t="n"/>
+      <c r="G80" s="52" t="n"/>
+      <c r="H80" s="52" t="n"/>
+      <c r="I80" s="52" t="n"/>
+      <c r="J80" s="52" t="n"/>
+      <c r="K80" s="52" t="n"/>
+      <c r="L80" s="52" t="n"/>
+      <c r="M80" s="52" t="n"/>
+      <c r="N80" s="52" t="n"/>
+      <c r="O80" s="52" t="n"/>
+      <c r="P80" s="53" t="n"/>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="77" t="inlineStr">
+        <is>
+          <t>Mortgage cash = Financial Plan mortgage written × yellow procuration % (default 0.35%) × (1 − 10% retention). 12-month view applies the 2-month lag, so Jan–Feb 2027 mortgage/protection cash is nil unless you model 2026 completions.</t>
+        </is>
+      </c>
+      <c r="B81" s="52" t="n"/>
+      <c r="C81" s="52" t="n"/>
+      <c r="D81" s="52" t="n"/>
+      <c r="E81" s="52" t="n"/>
+      <c r="F81" s="52" t="n"/>
+      <c r="G81" s="52" t="n"/>
+      <c r="H81" s="52" t="n"/>
+      <c r="I81" s="52" t="n"/>
+      <c r="J81" s="52" t="n"/>
+      <c r="K81" s="52" t="n"/>
+      <c r="L81" s="52" t="n"/>
+      <c r="M81" s="52" t="n"/>
+      <c r="N81" s="52" t="n"/>
+      <c r="O81" s="52" t="n"/>
+      <c r="P81" s="53" t="n"/>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="56" t="inlineStr">
+        <is>
+          <t>Network fee £75/week = £325/month is Confirmed. 10% mortgage and 15% protection retention are Confirmed (Ahmed Bawa, 2 Sep 2026).</t>
+        </is>
+      </c>
+      <c r="B82" s="52" t="n"/>
+      <c r="C82" s="52" t="n"/>
+      <c r="D82" s="52" t="n"/>
+      <c r="E82" s="52" t="n"/>
+      <c r="F82" s="52" t="n"/>
+      <c r="G82" s="52" t="n"/>
+      <c r="H82" s="52" t="n"/>
+      <c r="I82" s="52" t="n"/>
+      <c r="J82" s="52" t="n"/>
+      <c r="K82" s="52" t="n"/>
+      <c r="L82" s="52" t="n"/>
+      <c r="M82" s="52" t="n"/>
+      <c r="N82" s="52" t="n"/>
+      <c r="O82" s="52" t="n"/>
+      <c r="P82" s="53" t="n"/>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="77" t="inlineStr">
+        <is>
+          <t>Sole trader vs limited company is still open (20 Aug consult). Wife is a teacher ~£25–26k and a possible shareholder — tax advice sits with the accountant, not this sheet.</t>
+        </is>
+      </c>
+      <c r="B83" s="52" t="n"/>
+      <c r="C83" s="52" t="n"/>
+      <c r="D83" s="52" t="n"/>
+      <c r="E83" s="52" t="n"/>
+      <c r="F83" s="52" t="n"/>
+      <c r="G83" s="52" t="n"/>
+      <c r="H83" s="52" t="n"/>
+      <c r="I83" s="52" t="n"/>
+      <c r="J83" s="52" t="n"/>
+      <c r="K83" s="52" t="n"/>
+      <c r="L83" s="52" t="n"/>
+      <c r="M83" s="52" t="n"/>
+      <c r="N83" s="52" t="n"/>
+      <c r="O83" s="52" t="n"/>
+      <c r="P83" s="53" t="n"/>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="56" t="inlineStr">
+        <is>
+          <t>Duncan &amp; Co FCA number stays TBC. Do not invent one. Host network is Rosemount Financial Solutions (IFA) Ltd FRN 535515.</t>
+        </is>
+      </c>
+      <c r="B84" s="52" t="n"/>
+      <c r="C84" s="52" t="n"/>
+      <c r="D84" s="52" t="n"/>
+      <c r="E84" s="52" t="n"/>
+      <c r="F84" s="52" t="n"/>
+      <c r="G84" s="52" t="n"/>
+      <c r="H84" s="52" t="n"/>
+      <c r="I84" s="52" t="n"/>
+      <c r="J84" s="52" t="n"/>
+      <c r="K84" s="52" t="n"/>
+      <c r="L84" s="52" t="n"/>
+      <c r="M84" s="52" t="n"/>
+      <c r="N84" s="52" t="n"/>
+      <c r="O84" s="52" t="n"/>
+      <c r="P84" s="53" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="17">
+    <mergeCell ref="A63:P63"/>
+    <mergeCell ref="A75:P75"/>
+    <mergeCell ref="A76:P76"/>
+    <mergeCell ref="A84:P84"/>
+    <mergeCell ref="A80:P80"/>
+    <mergeCell ref="A1:P2"/>
+    <mergeCell ref="A79:P79"/>
+    <mergeCell ref="A77:P77"/>
+    <mergeCell ref="A83:P83"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A78:P78"/>
+    <mergeCell ref="A82:P82"/>
+    <mergeCell ref="A81:P81"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <dataValidations count="2">
+    <dataValidation sqref="C20:C37 C42:C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Fixed,Variable,One-off"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C7:C16 D20:D37 D42:D45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Confirmed,Estimate,TBC,Discussed,Formula,Linked"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3293,23 +5815,444 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="79" t="inlineStr">
+        <is>
+          <t>2027 Quarterly Planner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1"/>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="80" t="inlineStr">
+        <is>
+          <t>Duncan &amp; Co launch year. Keep actions compact. Yellow cells stay editable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="81" t="n"/>
+      <c r="B4" s="81" t="n"/>
+      <c r="C4" s="81" t="n"/>
+      <c r="D4" s="81" t="n"/>
+      <c r="E4" s="81" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Annual goals</t>
+        </is>
+      </c>
+      <c r="B5" s="61" t="n"/>
+      <c r="C5" s="60" t="inlineStr">
+        <is>
+          <t>Q1 — Jan to Mar 2027 (plus residual 2026 launch)</t>
+        </is>
+      </c>
+      <c r="D5" s="61" t="n"/>
+      <c r="E5" s="60" t="inlineStr">
+        <is>
+          <t>Q2 — Apr to Jun 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>Appoint with Rosemount as trading style and launch Duncan &amp; Co (own brand retained)</t>
+        </is>
+      </c>
+      <c r="B6" s="77" t="n"/>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>Finish refs, tests and DD; confirm Rosemount appointment (target end Sep 2026 if still open)</t>
+        </is>
+      </c>
+      <c r="D6" s="77" t="n"/>
+      <c r="E6" s="49" t="inlineStr">
+        <is>
+          <t>Review Q1 written vs cash (2-month banking lag)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>Deliver £12.42m mortgage and £2.88m protection written (Financial Plan targets)</t>
+        </is>
+      </c>
+      <c r="B7" s="77" t="n"/>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>Sign working SLAs with DJ Alexander and Hannah Fraser</t>
+        </is>
+      </c>
+      <c r="D7" s="77" t="n"/>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>Close or park Ralph’s Thayer (Ivan Ralph) outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>Build toward £80–120k year-1 cash after 10% / 15% network retention — see Monthly Costs</t>
+        </is>
+      </c>
+      <c r="B8" s="77" t="n"/>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>Website live or Business Gateway grant outcome recorded</t>
+        </is>
+      </c>
+      <c r="D8" s="77" t="n"/>
+      <c r="E8" s="49" t="inlineStr">
+        <is>
+          <t>Measure protection attachment on completions</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>Convert DJ Alexander, Hannah Fraser and Ralph’s Thayer into live introducer flow</t>
+        </is>
+      </c>
+      <c r="B9" s="77" t="n"/>
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>Intelligent Office + Mortgage Brain live; write the client journey</t>
+        </is>
+      </c>
+      <c r="D9" s="77" t="n"/>
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t>Accountant introduction route live via self-employed cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>Stand up website (Business Gateway grant) and Intelligent Office client journey</t>
+        </is>
+      </c>
+      <c r="B10" s="77" t="n"/>
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>Attend Rosemount protection workshops; start Beanstalk JISA partnership</t>
+        </is>
+      </c>
+      <c r="D10" s="77" t="n"/>
+      <c r="E10" s="49" t="inlineStr">
+        <is>
+          <t>Glasgow exclusive: confirm in writing or treat as parked / high risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>Decide AR vs trading-style only if the Glasgow exclusive actually lands</t>
+        </is>
+      </c>
+      <c r="B11" s="77" t="n"/>
+      <c r="C11" s="49" t="n"/>
+      <c r="D11" s="77" t="n"/>
+      <c r="E11" s="49" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="81" t="n"/>
+      <c r="B12" s="81" t="n"/>
+      <c r="C12" s="81" t="n"/>
+      <c r="D12" s="81" t="n"/>
+      <c r="E12" s="81" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="81" t="n"/>
+      <c r="B13" s="81" t="n"/>
+      <c r="C13" s="60" t="inlineStr">
+        <is>
+          <t>Q3 — Jul to Sep 2027</t>
+        </is>
+      </c>
+      <c r="D13" s="61" t="n"/>
+      <c r="E13" s="60" t="inlineStr">
+        <is>
+          <t>Q4 — Oct to Dec 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="81" t="n"/>
+      <c r="B14" s="81" t="n"/>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>Mid-year cash vs £80–120k ambition using Monthly Costs</t>
+        </is>
+      </c>
+      <c r="D14" s="77" t="n"/>
+      <c r="E14" s="49" t="inlineStr">
+        <is>
+          <t>Close remaining mortgage and protection written gaps</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="81" t="n"/>
+      <c r="B15" s="81" t="n"/>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>AR decision if Glasgow volume is real enough for extra advisers</t>
+        </is>
+      </c>
+      <c r="D15" s="77" t="n"/>
+      <c r="E15" s="49" t="inlineStr">
+        <is>
+          <t>2028 plan: sole trader vs limited company; wife as possible shareholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="81" t="n"/>
+      <c r="B16" s="81" t="n"/>
+      <c r="C16" s="49" t="inlineStr">
+        <is>
+          <t>International advice: Rosemount permission granted or stay refer-only</t>
+        </is>
+      </c>
+      <c r="D16" s="77" t="n"/>
+      <c r="E16" s="49" t="inlineStr">
+        <is>
+          <t>Tesla lease amount confirmed; company-transfer decision with lessor</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="81" t="n"/>
+      <c r="B17" s="81" t="n"/>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>BoE hold / cut / rise CRM cadence proven in Intelligent Office</t>
+        </is>
+      </c>
+      <c r="D17" s="77" t="n"/>
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t>Annual introducer reviews (DJ Alexander, Hannah Fraser, others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="81" t="n"/>
+      <c r="B18" s="81" t="n"/>
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>Add a case manager only if sole-adviser capacity breaks</t>
+        </is>
+      </c>
+      <c r="D18" s="77" t="n"/>
+      <c r="E18" s="49" t="inlineStr">
+        <is>
+          <t>Hold annual planning review and lock 2028 budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="81" t="n"/>
+      <c r="B19" s="81" t="n"/>
+      <c r="C19" s="81" t="n"/>
+      <c r="D19" s="81" t="n"/>
+      <c r="E19" s="81" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="80" t="inlineStr">
+        <is>
+          <t>Informed by: 20 Aug 2026 structure consult; 2 Sep Rosemount (Ahmed Bawa); 2 Sep Ivan Ralph outreach; 3 Sep Business Gateway; 26 Aug rate-email / Tribe compliance notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="81" t="n"/>
+      <c r="B22" s="81" t="n"/>
+      <c r="C22" s="81" t="n"/>
+      <c r="D22" s="81" t="n"/>
+      <c r="E22" s="81" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="81" t="n"/>
+      <c r="B23" s="81" t="n"/>
+      <c r="C23" s="81" t="n"/>
+      <c r="D23" s="81" t="n"/>
+      <c r="E23" s="81" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="81" t="n"/>
+      <c r="B24" s="81" t="n"/>
+      <c r="C24" s="81" t="n"/>
+      <c r="D24" s="81" t="n"/>
+      <c r="E24" s="81" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="81" t="n"/>
+      <c r="B25" s="81" t="n"/>
+      <c r="C25" s="81" t="n"/>
+      <c r="D25" s="81" t="n"/>
+      <c r="E25" s="81" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="81" t="n"/>
+      <c r="B26" s="81" t="n"/>
+      <c r="C26" s="81" t="n"/>
+      <c r="D26" s="81" t="n"/>
+      <c r="E26" s="81" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="81" t="n"/>
+      <c r="B27" s="81" t="n"/>
+      <c r="C27" s="81" t="n"/>
+      <c r="D27" s="81" t="n"/>
+      <c r="E27" s="81" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="81" t="n"/>
+      <c r="B28" s="81" t="n"/>
+      <c r="C28" s="81" t="n"/>
+      <c r="D28" s="81" t="n"/>
+      <c r="E28" s="81" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="81" t="n"/>
+      <c r="B29" s="81" t="n"/>
+      <c r="C29" s="81" t="n"/>
+      <c r="D29" s="81" t="n"/>
+      <c r="E29" s="81" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="81" t="n"/>
+      <c r="B30" s="81" t="n"/>
+      <c r="C30" s="81" t="n"/>
+      <c r="D30" s="81" t="n"/>
+      <c r="E30" s="81" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="81" t="n"/>
+      <c r="B31" s="81" t="n"/>
+      <c r="C31" s="81" t="n"/>
+      <c r="D31" s="81" t="n"/>
+      <c r="E31" s="81" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="81" t="n"/>
+      <c r="B32" s="81" t="n"/>
+      <c r="C32" s="81" t="n"/>
+      <c r="D32" s="81" t="n"/>
+      <c r="E32" s="81" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="81" t="n"/>
+      <c r="B33" s="81" t="n"/>
+      <c r="C33" s="81" t="n"/>
+      <c r="D33" s="81" t="n"/>
+      <c r="E33" s="81" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="81" t="n"/>
+      <c r="B34" s="81" t="n"/>
+      <c r="C34" s="81" t="n"/>
+      <c r="D34" s="81" t="n"/>
+      <c r="E34" s="81" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="81" t="n"/>
+      <c r="B35" s="81" t="n"/>
+      <c r="C35" s="81" t="n"/>
+      <c r="D35" s="81" t="n"/>
+      <c r="E35" s="81" t="n"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="81" t="n"/>
+      <c r="B36" s="81" t="n"/>
+      <c r="C36" s="81" t="n"/>
+      <c r="D36" s="81" t="n"/>
+      <c r="E36" s="81" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="81" t="n"/>
+      <c r="B37" s="81" t="n"/>
+      <c r="C37" s="81" t="n"/>
+      <c r="D37" s="81" t="n"/>
+      <c r="E37" s="81" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="81" t="n"/>
+      <c r="B38" s="81" t="n"/>
+      <c r="C38" s="81" t="n"/>
+      <c r="D38" s="81" t="n"/>
+      <c r="E38" s="81" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="81" t="n"/>
+      <c r="B39" s="81" t="n"/>
+      <c r="C39" s="81" t="n"/>
+      <c r="D39" s="81" t="n"/>
+      <c r="E39" s="81" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="81" t="n"/>
+      <c r="B40" s="81" t="n"/>
+      <c r="C40" s="81" t="n"/>
+      <c r="D40" s="81" t="n"/>
+      <c r="E40" s="81" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A20:E21"/>
+    <mergeCell ref="A5"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="2" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="58" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>Consolidated Strategy Plan</t>
         </is>
@@ -3370,306 +6313,466 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="96" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Objectives</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>Turnover; banked target; productivity; adviser count; conversion</t>
-        </is>
-      </c>
-      <c r="F6" s="36" t="n"/>
-      <c r="G6" s="36" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>New firm after redundancy from Rettie (protected conversation Aug 2026). No client bank. Year-1 cash ambition £80–120k.</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>Launch Duncan &amp; Co; hit written targets and build toward £80–120k net cash.</t>
+        </is>
+      </c>
+      <c r="D6" s="49" t="inlineStr">
+        <is>
+          <t>Complete Rosemount appointment; lock introducers; run an activity-first first year; review AR only if Glasgow lands.</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="inlineStr">
+        <is>
+          <t>£12.42m mortgage / £2.88m protection written; £80–120k cash</t>
+        </is>
+      </c>
+      <c r="F6" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G6" s="49" t="inlineStr">
+        <is>
+          <t>All Year</t>
+        </is>
+      </c>
+      <c r="H6" s="49" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I6" s="36" t="inlineStr">
+        <is>
+          <t>12-month vision; turnover and banked targets; adviser growth; productivity; written-to-banked conversion; customer journey and KPIs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="96" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>Solo launch. Later AR status only if advisers are recruited (needed for Glasgow-scale volume).</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>Stay solo unless an exclusive Glasgow introducer is signed (that path could support 3–4 advisers).</t>
+        </is>
+      </c>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>Do not hire until volume is confirmed in writing; agree AR transition steps with Rosemount if it lands.</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="inlineStr">
+        <is>
+          <t>Adviser count = 1 unless Glasgow exclusive signed</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G7" s="49" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="H7" s="49" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>Current adviser levels and locations; employed/self-employed model; contracts and packages; academy options; recruitment activity and resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Lead Generation</t>
+        </is>
+      </c>
+      <c r="B8" s="49" t="inlineStr">
+        <is>
+          <t>DJ Alexander primary Edinburgh &amp; Glasgow; Hannah Fraser agreed primary Edinburgh solicitor/property; Ivan Ralph outreach started; Glasgow agency unconfirmed.</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>Diversify so no single introducer dominates; add website, accountants and BoE CRM.</t>
+        </is>
+      </c>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>Formalise DJ Alexander and Hannah Fraser; follow up Ivan Ralph; Business Gateway website; BoE rate emails.</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="inlineStr">
+        <is>
+          <t>Live introducer SLAs; volume/close rates in Overview (yellow TBC)</t>
+        </is>
+      </c>
+      <c r="F8" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G8" s="49" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="H6" s="36" t="inlineStr">
+      <c r="H8" s="49" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>Current and new lead sources; introducers; digital tools; volume and value by stream; ownership and support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>Rosemount protection workshops fortnightly; 15% net retention. Written target £240k/month is NOT cash.</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>High attachment on every mortgage; attend workshops; use Solution Builder / UnderwriteMe / iPipeline.</t>
+        </is>
+      </c>
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>Build protection into the client journey; track attachment % on the KPI Tracker.</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
+        <is>
+          <t>£240k/month written; cash via Monthly Costs £3,000 assumption</t>
+        </is>
+      </c>
+      <c r="F9" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G9" s="49" t="inlineStr">
+        <is>
+          <t>All Year</t>
+        </is>
+      </c>
+      <c r="H9" s="49" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="I6" s="36" t="inlineStr">
-        <is>
-          <t>12-month vision; turnover and banked targets; adviser growth; productivity; written-to-banked conversion; customer journey and KPIs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>Recruitment</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="inlineStr">
-        <is>
-          <t>Adviser count; hires; time to hire; employment mix</t>
-        </is>
-      </c>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="inlineStr">
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>Current mix and penetration; sales/referral model; triggers; commission splits; SLAs; development; client-bank campaigns; benchmark actions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>GI</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="inlineStr">
+        <is>
+          <t>No GI book. Other Income starter £1,500/month covers GI, referrals and Beanstalk JISA.</t>
+        </is>
+      </c>
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>Establish a GI referral route and switch on the Beanstalk JISA partnership.</t>
+        </is>
+      </c>
+      <c r="D10" s="49" t="inlineStr">
+        <is>
+          <t>Confirm GI panel/referral with Rosemount; set an offer-stage trigger.</t>
+        </is>
+      </c>
+      <c r="E10" s="49" t="inlineStr">
+        <is>
+          <t>£1,500/month Other Income starter</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G10" s="49" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H10" s="49" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I10" s="36" t="inlineStr">
+        <is>
+          <t>Current and target GI penetration; specialist/referral model; triggers; VITA options; commission splits; SLAs; development opportunities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Client Bank</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>No personal client bank; pipeline not novated from Rettie / Carrington.</t>
+        </is>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>Build a new bank from introducer completions in Intelligent Office.</t>
+        </is>
+      </c>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>IO CRM setup; BoE hold/cut/rise emails; annual-review process from first completions.</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="inlineStr">
+        <is>
+          <t>PED retention and review % once a book exists</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G11" s="49" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H11" s="49" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>Client nurture; PED management and retention; annual reviews; OOCB reports/campaigns; communications; specialist support; KPIs and conversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="96" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Admin &amp; Leads</t>
+        </is>
+      </c>
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>Self-admin at launch. Tools: Intelligent Office, Mortgage Brain, Solution Builder / UnderwriteMe / iPipeline.</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="inlineStr">
+        <is>
+          <t>Tight SLAs as sole adviser; add a case manager only if volume requires it.</t>
+        </is>
+      </c>
+      <c r="D12" s="49" t="inlineStr">
+        <is>
+          <t>Document the client journey; keep IO pipeline clean; keep the Overview hire rows as TBC.</t>
+        </is>
+      </c>
+      <c r="E12" s="49" t="inlineStr">
+        <is>
+          <t>Response SLA; completion time; quality</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G12" s="49" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="H7" s="36" t="inlineStr">
+      <c r="H12" s="49" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>Current adviser levels and locations; employed/self-employed model; contracts and packages; academy options; recruitment activity and resources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>Lead Generation</t>
-        </is>
-      </c>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="inlineStr">
-        <is>
-          <t>Lead volume; cost; appointment and completion conversion</t>
-        </is>
-      </c>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="inlineStr">
+      <c r="I12" s="36" t="inlineStr">
+        <is>
+          <t>Admin/case-manager resources and roles; workflow; lead management; nurture and qualification; overdue reviews; SLAs and incentives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="96" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>duncanandcofinancial.co.uk not yet built. Business Gateway funding discussed 3 Sep 2026.</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>Live site + light PPC + rate-triggered CRM emails.</t>
+        </is>
+      </c>
+      <c r="D13" s="49" t="inlineStr">
+        <is>
+          <t>Contact Business Gateway; set brand; load the three BoE scenario emails drafted 26 Aug.</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="inlineStr">
+        <is>
+          <t>Website/PPC leads; cost per lead</t>
+        </is>
+      </c>
+      <c r="F13" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G13" s="49" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="H8" s="36" t="inlineStr">
+      <c r="H13" s="49" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I13" s="36" t="inlineStr">
+        <is>
+          <t>Website/social audit; profile and lead generation support; ownership; PPC and campaigns; onboarding; Dashley/Mortgage Monitoring; digital toolkit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="96" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Wealth &amp; Later Life</t>
+        </is>
+      </c>
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Later-life / equity release TBC with Rosemount. International/overseas buyers still need compliance agreement.</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>Confirm permissions before any later-life or international advice; refer if not approved.</t>
+        </is>
+      </c>
+      <c r="D14" s="49" t="inlineStr">
+        <is>
+          <t>Agree later-life and international rules with Rosemount before the first case.</t>
+        </is>
+      </c>
+      <c r="E14" s="49" t="inlineStr">
+        <is>
+          <t>Zero unapproved advice; referral log if needed</t>
+        </is>
+      </c>
+      <c r="F14" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G14" s="49" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H14" s="49" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="I8" s="36" t="inlineStr">
-        <is>
-          <t>Current and new lead sources; introducers; digital tools; volume and value by stream; ownership and support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>Protection</t>
-        </is>
-      </c>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>Protection penetration; mix; referrals; SLA</t>
-        </is>
-      </c>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="H9" s="36" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I9" s="36" t="inlineStr">
-        <is>
-          <t>Current mix and penetration; sales/referral model; triggers; commission splits; SLAs; development; client-bank campaigns; benchmark actions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>GI</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>GI penetration; referrals; conversion; income</t>
-        </is>
-      </c>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="inlineStr">
+      <c r="I14" s="36" t="inlineStr">
+        <is>
+          <t>New/existing client opportunities; referral process and ownership; development and training; readiness milestones; interim referral approach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="96" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>Starter £1,500/month. Beanstalk JISA partnership available via Rosemount.</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>£18k Other Income across GI, Beanstalk, accountant intros and agreed referrals.</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="inlineStr">
+        <is>
+          <t>Beanstalk onboarding; accountant intros via self-employed cases; conveyancing/wills only if a panel exists.</t>
+        </is>
+      </c>
+      <c r="E15" s="49" t="inlineStr">
+        <is>
+          <t>£1,500/month default (Financial Plan yellow)</t>
+        </is>
+      </c>
+      <c r="F15" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G15" s="49" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="H10" s="36" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I10" s="36" t="inlineStr">
-        <is>
-          <t>Current and target GI penetration; specialist/referral model; triggers; VITA options; commission splits; SLAs; development opportunities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Client Bank</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>PED retention; annual reviews; campaigns; conversion</t>
-        </is>
-      </c>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="H11" s="36" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>Client nurture; PED management and retention; annual reviews; OOCB reports/campaigns; communications; specialist support; KPIs and conversion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>Admin &amp; Leads</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>Admin ratio; response SLA; completion time; quality</t>
-        </is>
-      </c>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="H12" s="36" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I12" s="36" t="inlineStr">
-        <is>
-          <t>Admin/case-manager resources and roles; workflow; lead management; nurture and qualification; overdue reviews; SLAs and incentives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>Website/PPC leads; cost per lead; engagement</t>
-        </is>
-      </c>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="H13" s="36" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I13" s="36" t="inlineStr">
-        <is>
-          <t>Website/social audit; profile and lead generation support; ownership; PPC and campaigns; onboarding; Dashley/Mortgage Monitoring; digital toolkit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>Wealth &amp; Later Life</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t>Opportunities; referrals; training; income</t>
-        </is>
-      </c>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="H14" s="36" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I14" s="36" t="inlineStr">
-        <is>
-          <t>New/existing client opportunities; referral process and ownership; development and training; readiness milestones; interim referral approach.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="inlineStr">
-        <is>
-          <t>Wealth; GI; conveyancing; wills; other referral income</t>
-        </is>
-      </c>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="H15" s="36" t="inlineStr">
+      <c r="H15" s="49" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
@@ -3697,15 +6800,16 @@
       <formula1>"Not Started,In Progress,At Risk,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
@@ -3720,7 +6824,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>2027 KPI Tracker</t>
         </is>
@@ -3816,9 +6920,7 @@
         <f>'Financial Plan'!D16</f>
         <v/>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>111243</v>
-      </c>
+      <c r="C6" s="55" t="n"/>
       <c r="D6" s="5">
         <f>IF(C6="","",C6-B6)</f>
         <v/>
@@ -3827,21 +6929,21 @@
         <f>'Financial Plan'!D13</f>
         <v/>
       </c>
-      <c r="F6" s="3" t="n"/>
+      <c r="F6" s="55" t="n"/>
       <c r="G6" s="5">
         <f>'Financial Plan'!D14</f>
         <v/>
       </c>
-      <c r="H6" s="3" t="n"/>
+      <c r="H6" s="55" t="n"/>
       <c r="I6" s="5">
         <f>'Financial Plan'!D15</f>
         <v/>
       </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="14" t="n"/>
-      <c r="N6" s="14" t="n"/>
+      <c r="J6" s="55" t="n"/>
+      <c r="K6" s="83" t="n"/>
+      <c r="L6" s="83" t="n"/>
+      <c r="M6" s="83" t="n"/>
+      <c r="N6" s="83" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3853,7 +6955,7 @@
         <f>'Financial Plan'!E16</f>
         <v/>
       </c>
-      <c r="C7" s="3" t="n"/>
+      <c r="C7" s="55" t="n"/>
       <c r="D7" s="5">
         <f>IF(C7="","",C7-B7)</f>
         <v/>
@@ -3862,21 +6964,21 @@
         <f>'Financial Plan'!E13</f>
         <v/>
       </c>
-      <c r="F7" s="3" t="n"/>
+      <c r="F7" s="55" t="n"/>
       <c r="G7" s="5">
         <f>'Financial Plan'!E14</f>
         <v/>
       </c>
-      <c r="H7" s="3" t="n"/>
+      <c r="H7" s="55" t="n"/>
       <c r="I7" s="5">
         <f>'Financial Plan'!E15</f>
         <v/>
       </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="14" t="n"/>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="14" t="n"/>
-      <c r="N7" s="14" t="n"/>
+      <c r="J7" s="55" t="n"/>
+      <c r="K7" s="83" t="n"/>
+      <c r="L7" s="83" t="n"/>
+      <c r="M7" s="83" t="n"/>
+      <c r="N7" s="83" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3888,7 +6990,7 @@
         <f>'Financial Plan'!F16</f>
         <v/>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="55" t="n"/>
       <c r="D8" s="5">
         <f>IF(C8="","",C8-B8)</f>
         <v/>
@@ -3897,21 +6999,21 @@
         <f>'Financial Plan'!F13</f>
         <v/>
       </c>
-      <c r="F8" s="3" t="n"/>
+      <c r="F8" s="55" t="n"/>
       <c r="G8" s="5">
         <f>'Financial Plan'!F14</f>
         <v/>
       </c>
-      <c r="H8" s="3" t="n"/>
+      <c r="H8" s="55" t="n"/>
       <c r="I8" s="5">
         <f>'Financial Plan'!F15</f>
         <v/>
       </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="14" t="n"/>
-      <c r="N8" s="14" t="n"/>
+      <c r="J8" s="55" t="n"/>
+      <c r="K8" s="83" t="n"/>
+      <c r="L8" s="83" t="n"/>
+      <c r="M8" s="83" t="n"/>
+      <c r="N8" s="83" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3923,7 +7025,7 @@
         <f>'Financial Plan'!G16</f>
         <v/>
       </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="55" t="n"/>
       <c r="D9" s="5">
         <f>IF(C9="","",C9-B9)</f>
         <v/>
@@ -3932,21 +7034,21 @@
         <f>'Financial Plan'!G13</f>
         <v/>
       </c>
-      <c r="F9" s="3" t="n"/>
+      <c r="F9" s="55" t="n"/>
       <c r="G9" s="5">
         <f>'Financial Plan'!G14</f>
         <v/>
       </c>
-      <c r="H9" s="3" t="n"/>
+      <c r="H9" s="55" t="n"/>
       <c r="I9" s="5">
         <f>'Financial Plan'!G15</f>
         <v/>
       </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="14" t="n"/>
+      <c r="J9" s="55" t="n"/>
+      <c r="K9" s="83" t="n"/>
+      <c r="L9" s="83" t="n"/>
+      <c r="M9" s="83" t="n"/>
+      <c r="N9" s="83" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3958,7 +7060,7 @@
         <f>'Financial Plan'!H16</f>
         <v/>
       </c>
-      <c r="C10" s="3" t="n"/>
+      <c r="C10" s="55" t="n"/>
       <c r="D10" s="5">
         <f>IF(C10="","",C10-B10)</f>
         <v/>
@@ -3967,21 +7069,21 @@
         <f>'Financial Plan'!H13</f>
         <v/>
       </c>
-      <c r="F10" s="3" t="n"/>
+      <c r="F10" s="55" t="n"/>
       <c r="G10" s="5">
         <f>'Financial Plan'!H14</f>
         <v/>
       </c>
-      <c r="H10" s="3" t="n"/>
+      <c r="H10" s="55" t="n"/>
       <c r="I10" s="5">
         <f>'Financial Plan'!H15</f>
         <v/>
       </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="14" t="n"/>
-      <c r="N10" s="14" t="n"/>
+      <c r="J10" s="55" t="n"/>
+      <c r="K10" s="83" t="n"/>
+      <c r="L10" s="83" t="n"/>
+      <c r="M10" s="83" t="n"/>
+      <c r="N10" s="83" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3993,7 +7095,7 @@
         <f>'Financial Plan'!I16</f>
         <v/>
       </c>
-      <c r="C11" s="3" t="n"/>
+      <c r="C11" s="55" t="n"/>
       <c r="D11" s="5">
         <f>IF(C11="","",C11-B11)</f>
         <v/>
@@ -4002,21 +7104,21 @@
         <f>'Financial Plan'!I13</f>
         <v/>
       </c>
-      <c r="F11" s="3" t="n"/>
+      <c r="F11" s="55" t="n"/>
       <c r="G11" s="5">
         <f>'Financial Plan'!I14</f>
         <v/>
       </c>
-      <c r="H11" s="3" t="n"/>
+      <c r="H11" s="55" t="n"/>
       <c r="I11" s="5">
         <f>'Financial Plan'!I15</f>
         <v/>
       </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="14" t="n"/>
-      <c r="N11" s="14" t="n"/>
+      <c r="J11" s="55" t="n"/>
+      <c r="K11" s="83" t="n"/>
+      <c r="L11" s="83" t="n"/>
+      <c r="M11" s="83" t="n"/>
+      <c r="N11" s="83" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4028,7 +7130,7 @@
         <f>'Financial Plan'!J16</f>
         <v/>
       </c>
-      <c r="C12" s="3" t="n"/>
+      <c r="C12" s="55" t="n"/>
       <c r="D12" s="5">
         <f>IF(C12="","",C12-B12)</f>
         <v/>
@@ -4037,21 +7139,21 @@
         <f>'Financial Plan'!J13</f>
         <v/>
       </c>
-      <c r="F12" s="3" t="n"/>
+      <c r="F12" s="55" t="n"/>
       <c r="G12" s="5">
         <f>'Financial Plan'!J14</f>
         <v/>
       </c>
-      <c r="H12" s="3" t="n"/>
+      <c r="H12" s="55" t="n"/>
       <c r="I12" s="5">
         <f>'Financial Plan'!J15</f>
         <v/>
       </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
-      <c r="N12" s="14" t="n"/>
+      <c r="J12" s="55" t="n"/>
+      <c r="K12" s="83" t="n"/>
+      <c r="L12" s="83" t="n"/>
+      <c r="M12" s="83" t="n"/>
+      <c r="N12" s="83" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4063,7 +7165,7 @@
         <f>'Financial Plan'!K16</f>
         <v/>
       </c>
-      <c r="C13" s="3" t="n"/>
+      <c r="C13" s="55" t="n"/>
       <c r="D13" s="5">
         <f>IF(C13="","",C13-B13)</f>
         <v/>
@@ -4072,21 +7174,21 @@
         <f>'Financial Plan'!K13</f>
         <v/>
       </c>
-      <c r="F13" s="3" t="n"/>
+      <c r="F13" s="55" t="n"/>
       <c r="G13" s="5">
         <f>'Financial Plan'!K14</f>
         <v/>
       </c>
-      <c r="H13" s="3" t="n"/>
+      <c r="H13" s="55" t="n"/>
       <c r="I13" s="5">
         <f>'Financial Plan'!K15</f>
         <v/>
       </c>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="14" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="14" t="n"/>
-      <c r="N13" s="14" t="n"/>
+      <c r="J13" s="55" t="n"/>
+      <c r="K13" s="83" t="n"/>
+      <c r="L13" s="83" t="n"/>
+      <c r="M13" s="83" t="n"/>
+      <c r="N13" s="83" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4098,7 +7200,7 @@
         <f>'Financial Plan'!L16</f>
         <v/>
       </c>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="55" t="n"/>
       <c r="D14" s="5">
         <f>IF(C14="","",C14-B14)</f>
         <v/>
@@ -4107,21 +7209,21 @@
         <f>'Financial Plan'!L13</f>
         <v/>
       </c>
-      <c r="F14" s="3" t="n"/>
+      <c r="F14" s="55" t="n"/>
       <c r="G14" s="5">
         <f>'Financial Plan'!L14</f>
         <v/>
       </c>
-      <c r="H14" s="3" t="n"/>
+      <c r="H14" s="55" t="n"/>
       <c r="I14" s="5">
         <f>'Financial Plan'!L15</f>
         <v/>
       </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="14" t="n"/>
-      <c r="L14" s="14" t="n"/>
-      <c r="M14" s="14" t="n"/>
-      <c r="N14" s="14" t="n"/>
+      <c r="J14" s="55" t="n"/>
+      <c r="K14" s="83" t="n"/>
+      <c r="L14" s="83" t="n"/>
+      <c r="M14" s="83" t="n"/>
+      <c r="N14" s="83" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4133,7 +7235,7 @@
         <f>'Financial Plan'!M16</f>
         <v/>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="55" t="n"/>
       <c r="D15" s="5">
         <f>IF(C15="","",C15-B15)</f>
         <v/>
@@ -4142,21 +7244,21 @@
         <f>'Financial Plan'!M13</f>
         <v/>
       </c>
-      <c r="F15" s="3" t="n"/>
+      <c r="F15" s="55" t="n"/>
       <c r="G15" s="5">
         <f>'Financial Plan'!M14</f>
         <v/>
       </c>
-      <c r="H15" s="3" t="n"/>
+      <c r="H15" s="55" t="n"/>
       <c r="I15" s="5">
         <f>'Financial Plan'!M15</f>
         <v/>
       </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="14" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="14" t="n"/>
-      <c r="N15" s="14" t="n"/>
+      <c r="J15" s="55" t="n"/>
+      <c r="K15" s="83" t="n"/>
+      <c r="L15" s="83" t="n"/>
+      <c r="M15" s="83" t="n"/>
+      <c r="N15" s="83" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4168,7 +7270,7 @@
         <f>'Financial Plan'!N16</f>
         <v/>
       </c>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="55" t="n"/>
       <c r="D16" s="5">
         <f>IF(C16="","",C16-B16)</f>
         <v/>
@@ -4177,21 +7279,21 @@
         <f>'Financial Plan'!N13</f>
         <v/>
       </c>
-      <c r="F16" s="3" t="n"/>
+      <c r="F16" s="55" t="n"/>
       <c r="G16" s="5">
         <f>'Financial Plan'!N14</f>
         <v/>
       </c>
-      <c r="H16" s="3" t="n"/>
+      <c r="H16" s="55" t="n"/>
       <c r="I16" s="5">
         <f>'Financial Plan'!N15</f>
         <v/>
       </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
+      <c r="J16" s="55" t="n"/>
+      <c r="K16" s="83" t="n"/>
+      <c r="L16" s="83" t="n"/>
+      <c r="M16" s="83" t="n"/>
+      <c r="N16" s="83" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4203,7 +7305,7 @@
         <f>'Financial Plan'!O16</f>
         <v/>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="55" t="n"/>
       <c r="D17" s="5">
         <f>IF(C17="","",C17-B17)</f>
         <v/>
@@ -4212,21 +7314,21 @@
         <f>'Financial Plan'!O13</f>
         <v/>
       </c>
-      <c r="F17" s="3" t="n"/>
+      <c r="F17" s="55" t="n"/>
       <c r="G17" s="5">
         <f>'Financial Plan'!O14</f>
         <v/>
       </c>
-      <c r="H17" s="3" t="n"/>
+      <c r="H17" s="55" t="n"/>
       <c r="I17" s="5">
         <f>'Financial Plan'!O15</f>
         <v/>
       </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="14" t="n"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="14" t="n"/>
+      <c r="J17" s="55" t="n"/>
+      <c r="K17" s="83" t="n"/>
+      <c r="L17" s="83" t="n"/>
+      <c r="M17" s="83" t="n"/>
+      <c r="N17" s="83" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
@@ -4297,15 +7399,16 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
@@ -4321,7 +7424,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>Risks, Actions and Model Checks</t>
         </is>
@@ -4509,545 +7612,633 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="inlineStr">
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="49" t="inlineStr">
+        <is>
+          <t>Rosemount appointment slips past end of September 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D17" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t>Complete references, tests and due diligence immediately; keep Ahmed Bawa updated weekly.</t>
+        </is>
+      </c>
+      <c r="F17" s="49" t="inlineStr">
+        <is>
+          <t>Bob / Rosemount (Ahmed Bawa)</t>
+        </is>
+      </c>
+      <c r="G17" s="84" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H17" s="49" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I17" s="49" t="inlineStr">
+        <is>
+          <t>Exploratory meeting 2 Sep 2026. Own brand retained as trading style. Do not invent an FCA number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="49" t="inlineStr">
+        <is>
+          <t>12-month non-compete / redundancy terms still in negotiation</t>
+        </is>
+      </c>
+      <c r="B18" s="49" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D18" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E18" s="49" t="inlineStr">
+        <is>
+          <t>Solicitor Donald to conclude protected-conversation terms. Do not solicit Rettie clients.</t>
+        </is>
+      </c>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t>Donald (solicitor) / Bob</t>
+        </is>
+      </c>
+      <c r="G18" s="84" t="n">
+        <v>46326</v>
+      </c>
+      <c r="H18" s="49" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I18" s="49" t="inlineStr">
+        <is>
+          <t>Protected conversation August 2026. Pipeline not novated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="49" t="inlineStr">
+        <is>
+          <t>No client bank — starting from zero</t>
+        </is>
+      </c>
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D19" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E19" s="49" t="inlineStr">
+        <is>
+          <t>Activity-first first year. Convert introducers before relying on reviews or PED.</t>
+        </is>
+      </c>
+      <c r="F19" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G19" s="84" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H19" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I19" s="49" t="inlineStr">
+        <is>
+          <t>Rosemount: first year is hardest; be proactive on activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>Introducer concentration on DJ Alexander and Hannah Fraser</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D20" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t>Put SLAs in writing. Add Ralph’s Thayer, accountants, website and BoE CRM so one source cannot stall the year.</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G20" s="84" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H20" s="49" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I20" s="49" t="inlineStr">
+        <is>
+          <t>Both named as primary. Volume still TBC on Business Overview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="49" t="inlineStr">
+        <is>
+          <t>Glasgow exclusive agency unconfirmed — capacity / AR risk</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D21" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E21" s="49" t="inlineStr">
+        <is>
+          <t>Do not hire or move to AR until the exclusive is signed. Treat 2,000–3,000 homes/year as high-risk.</t>
+        </is>
+      </c>
+      <c r="F21" s="49" t="inlineStr">
+        <is>
+          <t>Bob / DJ Alexander</t>
+        </is>
+      </c>
+      <c r="G21" s="84" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H21" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I21" s="49" t="inlineStr">
+        <is>
+          <t>Would be enough for 3–4 advisers IF it lands. Not confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="49" t="inlineStr">
+        <is>
+          <t>Trading-style vs appointed-representative status</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D22" s="49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E22" s="49" t="inlineStr">
+        <is>
+          <t>Launch as trading style under Rosemount. Revisit AR only if advisers are recruited.</t>
+        </is>
+      </c>
+      <c r="F22" s="49" t="inlineStr">
+        <is>
+          <t>Bob / Rosemount</t>
+        </is>
+      </c>
+      <c r="G22" s="84" t="n">
+        <v>46568</v>
+      </c>
+      <c r="H22" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I22" s="49" t="inlineStr">
+        <is>
+          <t>Ahmed Bawa: AR needed for Glasgow-scale volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>Onboarding references, tests and due diligence</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C17" s="36" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D23" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>Diary the tests; chase references; complete the DD pack for end-September appointment.</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G23" s="84" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H23" s="49" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I23" s="49" t="inlineStr">
+        <is>
+          <t>Appointment possible end Sep 2026 subject to refs / tests / DD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t>International / overseas buyer advice rules not yet agreed</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D17" s="36" t="inlineStr">
+      <c r="D24" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>No international advice until Rosemount compliance confirms. Refer if needed.</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t>Bob / Rosemount compliance</t>
+        </is>
+      </c>
+      <c r="G24" s="84" t="n">
+        <v>46387</v>
+      </c>
+      <c r="H24" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I24" s="49" t="inlineStr">
+        <is>
+          <t>Edinburgh and St Andrews demand discussed; permissions still TBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>First-year cash is tight until introducers convert (2-month lag)</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D25" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t>Hold a personal cash buffer. Overwrite Tesla and other yellow costs. Watch Monthly Costs net vs £80–120k.</t>
+        </is>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G25" s="84" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H25" s="49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I25" s="49" t="inlineStr">
+        <is>
+          <t>Do not treat £240k protection written as monthly cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>Tesla Model Y lease amount unknown; company transfer needs lessor approval</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="36" t="inlineStr">
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t>Get the exact monthly from the lessor. Ask about assignment to a limited company before incorporating around the car.</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G26" s="84" t="n">
+        <v>46326</v>
+      </c>
+      <c r="H26" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="I26" s="49" t="inlineStr">
+        <is>
+          <t>3 years remaining. Monthly Costs uses ~£550 estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>Website build funding not secured</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C27" s="49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="D27" s="49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="36" t="inlineStr">
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t>Contact Business Gateway. Do not commit the ~£2,500 build until grant / funding is known.</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G27" s="84" t="n">
+        <v>46326</v>
+      </c>
+      <c r="H27" s="49" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="I27" s="49" t="inlineStr">
+        <is>
+          <t>Discussed 3 Sep 2026. Launch cost is on Monthly Costs as Estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>Compliance bot / Tribe check not yet live</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C28" s="49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D19" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C20" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D20" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C21" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D21" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I21" s="36" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C22" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D22" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I22" s="36" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="36" t="n"/>
-      <c r="B23" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C23" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D23" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="36" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I23" s="36" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C24" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D24" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I24" s="36" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="36" t="n"/>
-      <c r="B25" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C25" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D25" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E25" s="36" t="n"/>
-      <c r="F25" s="36" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I25" s="36" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="36" t="n"/>
-      <c r="B26" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C26" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D26" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I26" s="36" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="36" t="n"/>
-      <c r="B27" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C27" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D27" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E27" s="36" t="n"/>
-      <c r="F27" s="36" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I27" s="36" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="36" t="n"/>
-      <c r="B28" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C28" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D28" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I28" s="36" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="36" t="n"/>
-      <c r="B29" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C29" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D29" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I29" s="36" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="36" t="n"/>
-      <c r="B30" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C30" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D30" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I30" s="36" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="36" t="n"/>
-      <c r="B31" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C31" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D31" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I31" s="36" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="36" t="n"/>
-      <c r="B32" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C32" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D32" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I32" s="36" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="36" t="n"/>
-      <c r="B33" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C33" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D33" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E33" s="36" t="n"/>
-      <c r="F33" s="36" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I33" s="36" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="36" t="n"/>
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C34" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I34" s="36" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="36" t="n"/>
-      <c r="B35" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C35" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D35" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E35" s="36" t="n"/>
-      <c r="F35" s="36" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I35" s="36" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="36" t="n"/>
-      <c r="B36" s="36" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C36" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D36" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="36" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I36" s="36" t="n"/>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
+        <is>
+          <t>Stand up the Tribe-document compliance Grokbot and switch on the automated Tribe check.</t>
+        </is>
+      </c>
+      <c r="F28" s="49" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="G28" s="84" t="n">
+        <v>46288</v>
+      </c>
+      <c r="H28" s="49" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I28" s="49" t="inlineStr">
+        <is>
+          <t>26 Aug notes: reminder ~four weeks later (around 23 Sep 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="49" t="n"/>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="54" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="49" t="n"/>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="54" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="49" t="n"/>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="54" t="n"/>
+      <c r="H31" s="49" t="n"/>
+      <c r="I31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="49" t="n"/>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="49" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="54" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="81" t="n"/>
+      <c r="B33" s="81" t="n"/>
+      <c r="C33" s="81" t="n"/>
+      <c r="D33" s="81" t="n"/>
+      <c r="E33" s="81" t="n"/>
+      <c r="F33" s="81" t="n"/>
+      <c r="G33" s="81" t="n"/>
+      <c r="H33" s="81" t="n"/>
+      <c r="I33" s="81" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="81" t="n"/>
+      <c r="B34" s="81" t="n"/>
+      <c r="C34" s="81" t="n"/>
+      <c r="D34" s="81" t="n"/>
+      <c r="E34" s="81" t="n"/>
+      <c r="F34" s="81" t="n"/>
+      <c r="G34" s="81" t="n"/>
+      <c r="H34" s="81" t="n"/>
+      <c r="I34" s="81" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="81" t="n"/>
+      <c r="B35" s="81" t="n"/>
+      <c r="C35" s="81" t="n"/>
+      <c r="D35" s="81" t="n"/>
+      <c r="E35" s="81" t="n"/>
+      <c r="F35" s="81" t="n"/>
+      <c r="G35" s="81" t="n"/>
+      <c r="H35" s="81" t="n"/>
+      <c r="I35" s="81" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="81" t="n"/>
+      <c r="B36" s="81" t="n"/>
+      <c r="C36" s="81" t="n"/>
+      <c r="D36" s="81" t="n"/>
+      <c r="E36" s="81" t="n"/>
+      <c r="F36" s="81" t="n"/>
+      <c r="G36" s="81" t="n"/>
+      <c r="H36" s="81" t="n"/>
+      <c r="I36" s="81" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5070,6 +8261,7 @@
       <formula1>"Open,In Progress,At Risk,Blocked,Complete,Closed"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -113,7 +113,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -198,6 +198,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4CC"/>
+        <bgColor rgb="00FFF4CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -441,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -652,6 +658,9 @@
     </xf>
     <xf numFmtId="167" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1475,9 +1484,9 @@
           <t>Previous firm / network</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
-        <is>
-          <t>Rettie Financial Services Ltd / Carrington Mortgage UK Ltd (MAB appointed representative)</t>
+      <c r="B7" s="85" t="inlineStr">
+        <is>
+          <t>Rettie Financial Services (5 years); previously Simpson &amp; Marwick, then one year in Aberdeen</t>
         </is>
       </c>
       <c r="C7" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1502,9 +1502,9 @@
           <t>Business address</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>Edinburgh and East Lothian — meetings by appointment. Correspondence address TBC on incorporation. Robert.Duncan@duncanandcofinancial.co.uk | 07528523216</t>
+      <c r="B8" s="85" t="inlineStr">
+        <is>
+          <t>88 Bonaly Grove, Edinburgh, EH13 0QB</t>
         </is>
       </c>
       <c r="C8" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B7" s="85" t="inlineStr">
         <is>
-          <t>Rettie Financial Services (5 years); previously Simpson &amp; Marwick, then one year in Aberdeen</t>
+          <t>Rettie Financial Services (5 years, FRN 969595); previously Simpson &amp; Marwick, then one year in Aberdeen</t>
         </is>
       </c>
       <c r="C7" s="52" t="n"/>
@@ -1520,9 +1520,9 @@
           <t>FCA number</t>
         </is>
       </c>
-      <c r="B9" s="49" t="inlineStr">
-        <is>
-          <t>TBC — intending trading style under Rosemount Financial Solutions (IFA) Ltd FRN 535515</t>
+      <c r="B9" s="85" t="inlineStr">
+        <is>
+          <t>TBC — Rettie Financial Services was FRN 969595</t>
         </is>
       </c>
       <c r="C9" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B9" s="85" t="inlineStr">
         <is>
-          <t>TBC — Rettie Financial Services was FRN 969595</t>
+          <t>TBC — Duncan &amp; Co not yet set up (Rettie Financial Services was FRN 969595)</t>
         </is>
       </c>
       <c r="C9" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1538,9 +1538,9 @@
           <t>MAB FCA number</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
-        <is>
-          <t>N/A going forward (previous network MAB Limited FRN 455545; MAB Derby 466154)</t>
+      <c r="B10" s="85" t="inlineStr">
+        <is>
+          <t>TBC / don't know</t>
         </is>
       </c>
       <c r="C10" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1556,9 +1556,9 @@
           <t>L&amp;G master agency number</t>
         </is>
       </c>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B11" s="85" t="inlineStr">
+        <is>
+          <t>N/A — don't have one</t>
         </is>
       </c>
       <c r="C11" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1574,9 +1574,9 @@
           <t>MAB agency number</t>
         </is>
       </c>
-      <c r="B12" s="49" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B12" s="85" t="inlineStr">
+        <is>
+          <t>N/A — don't have one</t>
         </is>
       </c>
       <c r="C12" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1592,9 +1592,9 @@
           <t>Pipeline novated?</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
-        <is>
-          <t>No — no personal client bank to novate</t>
+      <c r="B13" s="85" t="inlineStr">
+        <is>
+          <t>No — none novated (pipeline issues)</t>
         </is>
       </c>
       <c r="C13" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1604,15 +1604,15 @@
       <c r="G13" s="52" t="n"/>
       <c r="H13" s="53" t="n"/>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Fee structure</t>
         </is>
       </c>
-      <c r="B14" s="49" t="inlineStr">
-        <is>
-          <t>Lender procuration + protection commission; client fees by agreement on complex / international cases</t>
+      <c r="B14" s="85" t="inlineStr">
+        <is>
+          <t>Standard purchase &amp; remortgage: £195 on application, £300 on offer. Debt consolidation / adverse: £495 on application, £500 on offer. International: £495 on application, £1,000 on offer.</t>
         </is>
       </c>
       <c r="C14" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1628,9 +1628,9 @@
           <t>Specialist licences required</t>
         </is>
       </c>
-      <c r="B15" s="49" t="inlineStr">
-        <is>
-          <t>CeMAP / Cert CII (MP). Later-life / equity release TBC with Rosemount</t>
+      <c r="B15" s="85" t="inlineStr">
+        <is>
+          <t>Mortgage and protection; bridging; buy-to-let and commercial (B&amp;C)</t>
         </is>
       </c>
       <c r="C15" s="52" t="n"/>
@@ -1640,6 +1640,8 @@
       <c r="G15" s="52" t="n"/>
       <c r="H15" s="53" t="n"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
@@ -1905,6 +1907,8 @@
       <c r="G31" s="36" t="n"/>
       <c r="H31" s="36" t="n"/>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="35" t="inlineStr">
         <is>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1640,8 +1640,6 @@
       <c r="G15" s="52" t="n"/>
       <c r="H15" s="53" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
@@ -1699,35 +1697,35 @@
       </c>
       <c r="B20" s="49" t="inlineStr">
         <is>
-          <t>Director / Key Individual</t>
-        </is>
-      </c>
-      <c r="C20" s="50" t="inlineStr">
+          <t>Director / Mortgage &amp; Protection Adviser</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D20" s="50" t="inlineStr">
+      <c r="D20" s="49" t="inlineStr">
         <is>
           <t>Self-employed</t>
         </is>
       </c>
-      <c r="E20" s="50" t="inlineStr">
-        <is>
-          <t>Edinburgh / East Lothian</t>
-        </is>
-      </c>
-      <c r="F20" s="50" t="inlineStr">
-        <is>
-          <t>CeMAP / Cert CII (MP)</t>
-        </is>
-      </c>
-      <c r="G20" s="50" t="inlineStr">
-        <is>
-          <t>Self (launch)</t>
-        </is>
-      </c>
-      <c r="H20" s="50" t="inlineStr">
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t>Mortgage, protection, bridging, BTL &amp; commercial</t>
+        </is>
+      </c>
+      <c r="G20" s="49" t="inlineStr">
+        <is>
+          <t>No (self at launch)</t>
+        </is>
+      </c>
+      <c r="H20" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1907,8 +1905,6 @@
       <c r="G31" s="36" t="n"/>
       <c r="H31" s="36" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="35" t="inlineStr">
         <is>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -447,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -662,6 +662,13 @@
     <xf numFmtId="0" fontId="9" fillId="18" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1732,88 +1739,24 @@
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="49" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="B21" s="49" t="inlineStr">
-        <is>
-          <t>Admin / Case Manager (future)</t>
-        </is>
-      </c>
-      <c r="C21" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D21" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E21" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F21" s="50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="H21" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="A21" s="86" t="n"/>
+      <c r="B21" s="86" t="n"/>
+      <c r="C21" s="86" t="n"/>
+      <c r="D21" s="86" t="n"/>
+      <c r="E21" s="86" t="n"/>
+      <c r="F21" s="86" t="n"/>
+      <c r="G21" s="86" t="n"/>
+      <c r="H21" s="86" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="49" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="B22" s="49" t="inlineStr">
-        <is>
-          <t>Adviser — AR transition (future)</t>
-        </is>
-      </c>
-      <c r="C22" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D22" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E22" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F22" s="50" t="inlineStr">
-        <is>
-          <t>CeMAP TBC</t>
-        </is>
-      </c>
-      <c r="G22" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="H22" s="50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="A22" s="86" t="n"/>
+      <c r="B22" s="86" t="n"/>
+      <c r="C22" s="86" t="n"/>
+      <c r="D22" s="86" t="n"/>
+      <c r="E22" s="86" t="n"/>
+      <c r="F22" s="86" t="n"/>
+      <c r="G22" s="86" t="n"/>
+      <c r="H22" s="86" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="36" t="n"/>
@@ -1825,35 +1768,51 @@
       <c r="G23" s="36" t="n"/>
       <c r="H23" s="36" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="36" t="n"/>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="36" t="n"/>
-      <c r="B25" s="36" t="n"/>
-      <c r="C25" s="36" t="n"/>
-      <c r="D25" s="36" t="n"/>
-      <c r="E25" s="36" t="n"/>
-      <c r="F25" s="36" t="n"/>
-      <c r="G25" s="36" t="n"/>
-      <c r="H25" s="36" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="36" t="n"/>
-      <c r="B26" s="36" t="n"/>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="60" t="inlineStr">
+        <is>
+          <t>Lead-out and commercial split</t>
+        </is>
+      </c>
+      <c r="B24" s="61" t="n"/>
+      <c r="C24" s="61" t="n"/>
+      <c r="D24" s="61" t="n"/>
+      <c r="E24" s="61" t="n"/>
+      <c r="F24" s="61" t="n"/>
+      <c r="G24" s="61" t="n"/>
+      <c r="H24" s="61" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="87" t="inlineStr">
+        <is>
+          <t>Duncan &amp; Co can pass leads out to specialist advisers (bridging, commercial, BTL, overflow or other work the firm does not keep) for an agreed commercial split.</t>
+        </is>
+      </c>
+      <c r="B25" s="76" t="n"/>
+      <c r="C25" s="76" t="n"/>
+      <c r="D25" s="76" t="n"/>
+      <c r="E25" s="76" t="n"/>
+      <c r="F25" s="76" t="n"/>
+      <c r="G25" s="76" t="n"/>
+      <c r="H25" s="76" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="63" t="inlineStr">
+        <is>
+          <t>Split terms</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>TBC — commercial split to be agreed per introducer / specialist (typical referral-out).</t>
+        </is>
+      </c>
+      <c r="C26" s="88" t="n"/>
+      <c r="D26" s="88" t="n"/>
+      <c r="E26" s="88" t="n"/>
+      <c r="F26" s="88" t="n"/>
+      <c r="G26" s="88" t="n"/>
+      <c r="H26" s="88" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="36" t="n"/>
@@ -2233,13 +2192,16 @@
       <c r="F47" s="36" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B26:H26"/>
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="A34:F34"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1774,13 +1774,13 @@
           <t>Lead-out and commercial split</t>
         </is>
       </c>
-      <c r="B24" s="61" t="n"/>
-      <c r="C24" s="61" t="n"/>
-      <c r="D24" s="61" t="n"/>
-      <c r="E24" s="61" t="n"/>
-      <c r="F24" s="61" t="n"/>
-      <c r="G24" s="61" t="n"/>
-      <c r="H24" s="61" t="n"/>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="52" t="n"/>
+      <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="53" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="87" t="inlineStr">
@@ -1788,13 +1788,13 @@
           <t>Duncan &amp; Co can pass leads out to specialist advisers (bridging, commercial, BTL, overflow or other work the firm does not keep) for an agreed commercial split.</t>
         </is>
       </c>
-      <c r="B25" s="76" t="n"/>
-      <c r="C25" s="76" t="n"/>
-      <c r="D25" s="76" t="n"/>
-      <c r="E25" s="76" t="n"/>
-      <c r="F25" s="76" t="n"/>
-      <c r="G25" s="76" t="n"/>
-      <c r="H25" s="76" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+      <c r="H25" s="53" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="63" t="inlineStr">
@@ -1804,15 +1804,15 @@
       </c>
       <c r="B26" s="49" t="inlineStr">
         <is>
-          <t>TBC — commercial split to be agreed per introducer / specialist (typical referral-out).</t>
-        </is>
-      </c>
-      <c r="C26" s="88" t="n"/>
-      <c r="D26" s="88" t="n"/>
-      <c r="E26" s="88" t="n"/>
-      <c r="F26" s="88" t="n"/>
-      <c r="G26" s="88" t="n"/>
-      <c r="H26" s="88" t="n"/>
+          <t>50/50 split. The customer remains a Duncan &amp; Co Financial customer.</t>
+        </is>
+      </c>
+      <c r="C26" s="52" t="n"/>
+      <c r="D26" s="52" t="n"/>
+      <c r="E26" s="52" t="n"/>
+      <c r="F26" s="52" t="n"/>
+      <c r="G26" s="52" t="n"/>
+      <c r="H26" s="53" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="36" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1906,7 +1906,7 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="49" t="inlineStr">
         <is>
-          <t>DJ Alexander / David Alexander</t>
+          <t>DJ Alexander</t>
         </is>
       </c>
       <c r="B36" s="49" t="inlineStr">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B36" s="49" t="inlineStr">
         <is>
-          <t>Email / phone introduction</t>
+          <t>Email introduction (Edinburgh &amp; Lothians)</t>
         </is>
       </c>
       <c r="C36" s="49" t="inlineStr">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C36" s="49" t="inlineStr">
         <is>
-          <t>Estate agency</t>
+          <t>Estate agent</t>
         </is>
       </c>
       <c r="D36" s="50" t="inlineStr">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1919,9 +1919,9 @@
           <t>Estate agent</t>
         </is>
       </c>
-      <c r="D36" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="D36" s="49" t="inlineStr">
+        <is>
+          <t>5–7 leads a month</t>
         </is>
       </c>
       <c r="E36" s="51" t="inlineStr">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -447,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -669,6 +669,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1924,9 +1927,9 @@
           <t>5–7 leads a month</t>
         </is>
       </c>
-      <c r="E36" s="51" t="inlineStr">
-        <is>
-          <t>TBC</t>
+      <c r="E36" s="89" t="inlineStr">
+        <is>
+          <t>1 in 3 conversion</t>
         </is>
       </c>
       <c r="F36" s="49" t="inlineStr">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1934,7 +1934,7 @@
       </c>
       <c r="F36" s="49" t="inlineStr">
         <is>
-          <t>Primary introducer Edinburgh &amp; Glasgow</t>
+          <t>David Alexander</t>
         </is>
       </c>
     </row>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -447,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -670,6 +670,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="12" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1941,226 +1944,74 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="49" t="inlineStr">
         <is>
+          <t>Thorntons Solicitors</t>
+        </is>
+      </c>
+      <c r="B37" s="86" t="n"/>
+      <c r="C37" s="49" t="inlineStr">
+        <is>
+          <t>Solicitor</t>
+        </is>
+      </c>
+      <c r="D37" s="49" t="inlineStr">
+        <is>
+          <t>3–7 leads a month</t>
+        </is>
+      </c>
+      <c r="E37" s="90" t="n"/>
+      <c r="F37" s="49" t="inlineStr">
+        <is>
           <t>Hannah Fraser</t>
         </is>
       </c>
-      <c r="B37" s="49" t="inlineStr">
-        <is>
-          <t>Email / phone introduction</t>
-        </is>
-      </c>
-      <c r="C37" s="49" t="inlineStr">
-        <is>
-          <t>Solicitor / property</t>
-        </is>
-      </c>
-      <c r="D37" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E37" s="51" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F37" s="49" t="inlineStr">
-        <is>
-          <t>Senior property partner; agreed primary Edinburgh introducer</t>
-        </is>
-      </c>
     </row>
     <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="49" t="inlineStr">
-        <is>
-          <t>Ralph’s Thayer (Ivan Ralph)</t>
-        </is>
-      </c>
-      <c r="B38" s="49" t="inlineStr">
-        <is>
-          <t>Referral partnership outreach</t>
-        </is>
-      </c>
-      <c r="C38" s="49" t="inlineStr">
-        <is>
-          <t>Referral partner</t>
-        </is>
-      </c>
-      <c r="D38" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E38" s="51" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F38" s="49" t="inlineStr">
-        <is>
-          <t>Outreach 2 Sep 2026 — not yet live</t>
-        </is>
-      </c>
+      <c r="A38" s="86" t="n"/>
+      <c r="B38" s="86" t="n"/>
+      <c r="C38" s="86" t="n"/>
+      <c r="D38" s="86" t="n"/>
+      <c r="E38" s="90" t="n"/>
+      <c r="F38" s="86" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="49" t="inlineStr">
-        <is>
-          <t>Glasgow letting / estate agency (via DJ Alexander)</t>
-        </is>
-      </c>
-      <c r="B39" s="49" t="inlineStr">
-        <is>
-          <t>IF confirmed — exclusive</t>
-        </is>
-      </c>
-      <c r="C39" s="49" t="inlineStr">
-        <is>
-          <t>Estate / lettings</t>
-        </is>
-      </c>
-      <c r="D39" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E39" s="51" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F39" s="49" t="inlineStr">
-        <is>
-          <t>~2,000–3,000 homes/year discussed; NOT confirmed; high risk</t>
-        </is>
-      </c>
+      <c r="A39" s="86" t="n"/>
+      <c r="B39" s="86" t="n"/>
+      <c r="C39" s="86" t="n"/>
+      <c r="D39" s="86" t="n"/>
+      <c r="E39" s="90" t="n"/>
+      <c r="F39" s="86" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="49" t="inlineStr">
-        <is>
-          <t>Website / PPC</t>
-        </is>
-      </c>
-      <c r="B40" s="49" t="inlineStr">
-        <is>
-          <t>Web form</t>
-        </is>
-      </c>
-      <c r="C40" s="49" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D40" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E40" s="51" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F40" s="49" t="inlineStr">
-        <is>
-          <t>Contact Business Gateway for build funding (3 Sep 2026)</t>
-        </is>
-      </c>
+      <c r="A40" s="86" t="n"/>
+      <c r="B40" s="86" t="n"/>
+      <c r="C40" s="86" t="n"/>
+      <c r="D40" s="86" t="n"/>
+      <c r="E40" s="90" t="n"/>
+      <c r="F40" s="86" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="49" t="inlineStr">
-        <is>
-          <t>BoE rate-triggered CRM emails</t>
-        </is>
-      </c>
-      <c r="B41" s="49" t="inlineStr">
-        <is>
-          <t>Email campaign (hold / cut / rise)</t>
-        </is>
-      </c>
-      <c r="C41" s="49" t="inlineStr">
-        <is>
-          <t>Own CRM</t>
-        </is>
-      </c>
-      <c r="D41" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E41" s="51" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F41" s="49" t="inlineStr">
-        <is>
-          <t>Intelligent Office sequences; drafted 26 Aug 2026</t>
-        </is>
-      </c>
+      <c r="A41" s="86" t="n"/>
+      <c r="B41" s="86" t="n"/>
+      <c r="C41" s="86" t="n"/>
+      <c r="D41" s="86" t="n"/>
+      <c r="E41" s="90" t="n"/>
+      <c r="F41" s="86" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="49" t="inlineStr">
-        <is>
-          <t>Accountant introductions</t>
-        </is>
-      </c>
-      <c r="B42" s="49" t="inlineStr">
-        <is>
-          <t>Professional referral</t>
-        </is>
-      </c>
-      <c r="C42" s="49" t="inlineStr">
-        <is>
-          <t>Accountant</t>
-        </is>
-      </c>
-      <c r="D42" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E42" s="51" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F42" s="49" t="inlineStr">
-        <is>
-          <t>Via self-employed / complex cases</t>
-        </is>
-      </c>
+      <c r="A42" s="86" t="n"/>
+      <c r="B42" s="86" t="n"/>
+      <c r="C42" s="86" t="n"/>
+      <c r="D42" s="86" t="n"/>
+      <c r="E42" s="90" t="n"/>
+      <c r="F42" s="86" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="49" t="inlineStr">
-        <is>
-          <t>International / overseas buyers</t>
-        </is>
-      </c>
-      <c r="B43" s="49" t="inlineStr">
-        <is>
-          <t>Introducer / website</t>
-        </is>
-      </c>
-      <c r="C43" s="49" t="inlineStr">
-        <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="D43" s="50" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="E43" s="51" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F43" s="49" t="inlineStr">
-        <is>
-          <t>Edinburgh &amp; St Andrews demand; compliance still to agree with Rosemount</t>
-        </is>
-      </c>
+      <c r="A43" s="86" t="n"/>
+      <c r="B43" s="86" t="n"/>
+      <c r="C43" s="86" t="n"/>
+      <c r="D43" s="86" t="n"/>
+      <c r="E43" s="90" t="n"/>
+      <c r="F43" s="86" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="36" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1947,7 +1947,11 @@
           <t>Thorntons Solicitors</t>
         </is>
       </c>
-      <c r="B37" s="86" t="n"/>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>Email introduction (Edinburgh &amp; Lothians)</t>
+        </is>
+      </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
           <t>Solicitor</t>
@@ -1958,7 +1962,11 @@
           <t>3–7 leads a month</t>
         </is>
       </c>
-      <c r="E37" s="90" t="n"/>
+      <c r="E37" s="89" t="inlineStr">
+        <is>
+          <t>1 in 3 conversion</t>
+        </is>
+      </c>
       <c r="F37" s="49" t="inlineStr">
         <is>
           <t>Hannah Fraser</t>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1974,10 +1974,22 @@
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="86" t="n"/>
-      <c r="B38" s="86" t="n"/>
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>TBC — system referral process</t>
+        </is>
+      </c>
+      <c r="B38" s="49" t="inlineStr">
+        <is>
+          <t>System-related referral process</t>
+        </is>
+      </c>
       <c r="C38" s="86" t="n"/>
-      <c r="D38" s="86" t="n"/>
+      <c r="D38" s="49" t="inlineStr">
+        <is>
+          <t>10–20 leads a week (estimate)</t>
+        </is>
+      </c>
       <c r="E38" s="90" t="n"/>
       <c r="F38" s="86" t="n"/>
     </row>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1984,7 +1984,11 @@
           <t>System-related referral process</t>
         </is>
       </c>
-      <c r="C38" s="86" t="n"/>
+      <c r="C38" s="49" t="inlineStr">
+        <is>
+          <t>Estate agent</t>
+        </is>
+      </c>
       <c r="D38" s="49" t="inlineStr">
         <is>
           <t>10–20 leads a week (estimate)</t>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1994,7 +1994,11 @@
           <t>10–20 leads a week (estimate)</t>
         </is>
       </c>
-      <c r="E38" s="90" t="n"/>
+      <c r="E38" s="89" t="inlineStr">
+        <is>
+          <t>1 in 3 conversion</t>
+        </is>
+      </c>
       <c r="F38" s="86" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1999,7 +1999,11 @@
           <t>1 in 3 conversion</t>
         </is>
       </c>
-      <c r="F38" s="86" t="n"/>
+      <c r="F38" s="49" t="inlineStr">
+        <is>
+          <t>No notes</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="86" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -1705,7 +1705,7 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="49" t="inlineStr">
         <is>
-          <t>Robert (Bob) Duncan</t>
+          <t>Robert Duncan</t>
         </is>
       </c>
       <c r="B20" s="49" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="B18" s="49" t="inlineStr">
         <is>
-          <t>Robert (Bob) Duncan</t>
+          <t>Robert Duncan</t>
         </is>
       </c>
       <c r="C18" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B19" s="54" t="n">
-        <v>46270</v>
+        <v>46300</v>
       </c>
       <c r="C19" s="52" t="n"/>
       <c r="D19" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -3599,12 +3599,12 @@
       </c>
       <c r="C12" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="D12" s="56" t="inlineStr">
         <is>
-          <t>Overwrite with actual lender mix. Not a Rosemount quote.</t>
+          <t>Robert Duncan: mortgage income is 0.35% of borrowing. Typical loan £180k–£250k.</t>
         </is>
       </c>
       <c r="E12" s="56" t="inlineStr">
@@ -3714,6 +3714,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="60" t="inlineStr">
         <is>
@@ -5550,7 +5551,7 @@
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="77" t="inlineStr">
         <is>
-          <t>Mortgage cash = Financial Plan mortgage written × yellow procuration % (default 0.35%) × (1 − 10% retention). 12-month view applies the 2-month lag, so Jan–Feb 2027 mortgage/protection cash is nil unless you model 2026 completions.</t>
+          <t>Typical completed mortgage: £180,000–£250,000. Income = 0.35% of that borrowing (confirmed by Robert).</t>
         </is>
       </c>
       <c r="B81" s="52" t="n"/>
@@ -5572,7 +5573,7 @@
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="56" t="inlineStr">
         <is>
-          <t>Network fee £75/week = £325/month is Confirmed. 10% mortgage and 15% protection retention are Confirmed (Ahmed Bawa, 2 Sep 2026).</t>
+          <t>Named sources only (DJ 5–7 + Thorntons 3–7, 1 in 3): about 3–5 completions/month. Mid written ≈ £790k; mid income before network ≈ £2,800.</t>
         </is>
       </c>
       <c r="B82" s="52" t="n"/>
@@ -5594,7 +5595,7 @@
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="77" t="inlineStr">
         <is>
-          <t>Sole trader vs limited company is still open (20 Aug consult). Wife is a teacher ~£25–26k and a possible shareholder — tax advice sits with the accountant, not this sheet.</t>
+          <t>If TBC system 10–20/week is included at 1 in 3, written jumps to several million a month. Decide whether that sits in the 2027 target.</t>
         </is>
       </c>
       <c r="B83" s="52" t="n"/>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -447,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -673,6 +673,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2805,15 +2808,15 @@
           <t>Mortgage</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>1035000</v>
+      <c r="B7" s="91" t="n">
+        <v>790000</v>
       </c>
       <c r="C7" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="38" t="inlineStr">
         <is>
-          <t>New Build and Retention combined</t>
+          <t>Named sources only (DJ Alexander + Thorntons). Mid-point of 3–5 completions × £180k–£250k. Income = 0.35% of this written amount.</t>
         </is>
       </c>
       <c r="E7" s="40" t="n"/>
@@ -3714,7 +3717,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="60" t="inlineStr">
         <is>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -2828,15 +2828,15 @@
           <t>Protection</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>240000</v>
+      <c r="B8" s="91" t="n">
+        <v>2000</v>
       </c>
       <c r="C8" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="38" t="inlineStr">
         <is>
-          <t>Protection income</t>
+          <t>Cash: £1,000 per protection case; 1–3 cases a month (mid £2,000). Not a large written-volume figure.</t>
         </is>
       </c>
       <c r="E8" s="40" t="n"/>
@@ -3623,16 +3623,16 @@
         </is>
       </c>
       <c r="B13" s="70" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="C13" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="D13" s="56" t="inlineStr">
         <is>
-          <t>Cash assumption — NOT the £240k protection written figure.</t>
+          <t>Robert: £1,000 per case, 1–3 cases a month. Mid-point £2,000 cash before 15% retention.</t>
         </is>
       </c>
       <c r="E13" s="56" t="inlineStr">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="B9" s="55" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="C9" s="36" t="n">
         <v>0</v>

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -3939,11 +3939,11 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="63" t="inlineStr">
         <is>
-          <t>Microsoft 365</t>
+          <t>Office subscription</t>
         </is>
       </c>
       <c r="B26" s="64" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C26" s="50" t="inlineStr">
         <is>
@@ -3952,12 +3952,12 @@
       </c>
       <c r="D26" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E26" s="56" t="inlineStr">
         <is>
-          <t>Business standard / equivalent.</t>
+          <t>Office subscription (Robert).</t>
         </is>
       </c>
       <c r="F26" s="66">
@@ -4026,11 +4026,11 @@
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="63" t="inlineStr">
         <is>
-          <t>Domain / email</t>
+          <t>Domain name and website</t>
         </is>
       </c>
       <c r="B29" s="64" t="n">
-        <v>15</v>
+        <v>14.99</v>
       </c>
       <c r="C29" s="50" t="inlineStr">
         <is>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="D29" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E29" s="56" t="inlineStr">
         <is>
-          <t>duncanandcofinancial.co.uk.</t>
+          <t>Domain name and website together.</t>
         </is>
       </c>
       <c r="F29" s="66">
@@ -4055,11 +4055,11 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="63" t="inlineStr">
         <is>
-          <t>Web hosting</t>
+          <t>Web hosting (included above)</t>
         </is>
       </c>
       <c r="B30" s="64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C30" s="50" t="inlineStr">
         <is>
@@ -4068,12 +4068,12 @@
       </c>
       <c r="D30" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E30" s="56" t="inlineStr">
         <is>
-          <t>If not bundled with the website grant.</t>
+          <t>Included in the £14.99 domain/website line.</t>
         </is>
       </c>
       <c r="F30" s="66">
@@ -4084,11 +4084,11 @@
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="63" t="inlineStr">
         <is>
-          <t>AI / productivity tools</t>
+          <t>AI package</t>
         </is>
       </c>
       <c r="B31" s="64" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
@@ -4097,12 +4097,12 @@
       </c>
       <c r="D31" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E31" s="56" t="inlineStr">
         <is>
-          <t>Grok / Cursor / similar.</t>
+          <t>AI package (Robert).</t>
         </is>
       </c>
       <c r="F31" s="66">
@@ -4229,11 +4229,11 @@
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="63" t="inlineStr">
         <is>
-          <t>Stationery / postage</t>
+          <t>Laptop (monthly)</t>
         </is>
       </c>
       <c r="B36" s="64" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C36" s="50" t="inlineStr">
         <is>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="D36" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E36" s="56" t="inlineStr">
         <is>
-          <t>IDV, packs, post.</t>
+          <t>Laptop on a monthly basis (Robert).</t>
         </is>
       </c>
       <c r="F36" s="66">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B42" s="70" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="D42" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Moved</t>
         </is>
       </c>
       <c r="E42" s="56" t="inlineStr">
         <is>
-          <t>Replace / dedicated work machine.</t>
+          <t>Laptop is £50/month in operating costs, not a one-off.</t>
         </is>
       </c>
       <c r="F42" s="56" t="inlineStr">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="B43" s="70" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="C43" s="50" t="inlineStr">
         <is>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="D43" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Included</t>
         </is>
       </c>
       <c r="E43" s="56" t="inlineStr">
         <is>
-          <t>Or Business Gateway funded — set to 0 if grant covers it.</t>
+          <t>Website is in the £14.99 monthly domain/website line.</t>
         </is>
       </c>
       <c r="F43" s="56" t="inlineStr">
@@ -4416,8 +4416,8 @@
           <t>Company formation</t>
         </is>
       </c>
-      <c r="B44" s="70" t="n">
-        <v>50</v>
+      <c r="B44" s="64" t="n">
+        <v>480</v>
       </c>
       <c r="C44" s="50" t="inlineStr">
         <is>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="D44" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E44" s="56" t="inlineStr">
         <is>
-          <t>If limited company route is chosen (20 Aug consult).</t>
+          <t>£400 + VAT for business registration and setup.</t>
         </is>
       </c>
       <c r="F44" s="56" t="inlineStr">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="B21" s="64" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="C21" s="50" t="inlineStr">
         <is>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="D21" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E21" s="56" t="inlineStr">
         <is>
-          <t>Amount UNKNOWN — 3 years remaining. Transfer needs lessor approval.</t>
+          <t>Tesla Model Y is in Robert’s personal name — not a business cost.</t>
         </is>
       </c>
       <c r="F21" s="66">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="B22" s="64" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C22" s="50" t="inlineStr">
         <is>
@@ -3836,12 +3836,12 @@
       </c>
       <c r="D22" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Ignored</t>
         </is>
       </c>
       <c r="E22" s="56" t="inlineStr">
         <is>
-          <t>Overwrite with actual schedule.</t>
+          <t>Ignored — not a business cost for this plan.</t>
         </is>
       </c>
       <c r="F22" s="66">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="B23" s="64" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
       </c>
       <c r="D23" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Ignored</t>
         </is>
       </c>
       <c r="E23" s="56" t="inlineStr">
         <is>
-          <t>Electricity for the Tesla; will vary.</t>
+          <t>Ignored — not a business cost for this plan.</t>
         </is>
       </c>
       <c r="F23" s="66">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -3894,12 +3894,12 @@
       </c>
       <c r="D24" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E24" s="56" t="inlineStr">
         <is>
-          <t>Business mobile.</t>
+          <t>£45/month — confirmed by Robert.</t>
         </is>
       </c>
       <c r="F24" s="66">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -3923,12 +3923,12 @@
       </c>
       <c r="D25" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E25" s="56" t="inlineStr">
         <is>
-          <t>Home-office share.</t>
+          <t>£30 home-office share — left as is by Robert.</t>
         </is>
       </c>
       <c r="F25" s="66">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -4010,12 +4010,12 @@
       </c>
       <c r="D28" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E28" s="56" t="inlineStr">
         <is>
-          <t>Monthly accrual; year-end extra not included.</t>
+          <t>£150/month accrual — confirmed by Robert.</t>
         </is>
       </c>
       <c r="F28" s="66">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -3981,12 +3981,12 @@
       </c>
       <c r="D27" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E27" s="56" t="inlineStr">
         <is>
-          <t>Bookkeeping subscription.</t>
+          <t>£33/month Xero — confirmed by Robert.</t>
         </is>
       </c>
       <c r="F27" s="66">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="B32" s="64" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="D32" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E32" s="56" t="inlineStr">
         <is>
-          <t>Light brand and lead support.</t>
+          <t>Set to £0 by Robert.</t>
         </is>
       </c>
       <c r="F32" s="66">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="B33" s="64" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="D33" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E33" s="56" t="inlineStr">
         <is>
-          <t>Keep modest in year 1.</t>
+          <t>Set to £0 by Robert.</t>
         </is>
       </c>
       <c r="F33" s="66">

--- a/duncan-and-co-planning/Strategic_planning.xlsx
+++ b/duncan-and-co-planning/Strategic_planning.xlsx
@@ -4184,12 +4184,12 @@
       </c>
       <c r="D34" s="50" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="E34" s="56" t="inlineStr">
         <is>
-          <t>Account fees.</t>
+          <t>£10/month bank fees — confirmed by Robert.</t>
         </is>
       </c>
       <c r="F34" s="66">
